--- a/static/uploads/Input.xlsx
+++ b/static/uploads/Input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sayanchatterjee/Nextcloud/Work/BlackCoffer/Data-Extraction-and-NLP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F195D18-2A56-6B40-9BEC-A2D3E1DCA809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD03B272-C7FE-484E-865D-69715139DB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>URL_ID</t>
   </si>
@@ -33,41 +33,59 @@
     <t>URL</t>
   </si>
   <si>
-    <t>Nasher Miles Bag</t>
+    <t>Nothing Phone 3a</t>
   </si>
   <si>
-    <t>https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1</t>
+    <t>https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2</t>
   </si>
   <si>
-    <t>Ugreen Charger</t>
+    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3</t>
   </si>
   <si>
-    <t>https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3</t>
+    <t>Sony PlayStation®5 Digital Edition (slim) Console Video Game</t>
   </si>
   <si>
-    <t>https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3</t>
+    <t>https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1</t>
   </si>
   <si>
-    <t>Iphone !6e</t>
+    <t>Samsung Galaxy S25 Ultra</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1</t>
+    <t>https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3</t>
   </si>
   <si>
-    <t>Samsung Galaxy S24 Ultra 5G</t>
+    <t>vivo X200 Pro</t>
   </si>
   <si>
-    <t>https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45</t>
+    <t>https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3</t>
   </si>
   <si>
-    <t>OnePlus Nord 4 5G (Obsidian Midnight, 8GB RAM, 256GB Storage)</t>
+    <t>https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>Xiaomi 15 Ultra</t>
+  </si>
+  <si>
+    <t>OnePlus 13</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>Motorola Razr 60 Ultra</t>
+  </si>
+  <si>
+    <t>Samsung S24 FE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +153,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -177,10 +203,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -192,8 +219,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -410,7 +439,7 @@
   <dimension ref="A1:Z932"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="1" max="1" width="52.1640625" customWidth="1"/>
     <col min="2" max="2" width="122.5" customWidth="1"/>
     <col min="3" max="26" width="8.6640625" customWidth="1"/>
   </cols>
@@ -449,10 +478,10 @@
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
+      <c r="B2" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -481,10 +510,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
+      <c r="B3" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -513,10 +542,10 @@
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -545,10 +574,10 @@
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -575,12 +604,12 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -608,8 +637,12 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
+      <c r="A7" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -636,8 +669,12 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>4</v>
+      </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -664,8 +701,12 @@
       <c r="Z8" s="3"/>
     </row>
     <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
+      <c r="A9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>6</v>
+      </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -26536,6 +26577,9 @@
       <c r="Z932" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1" display="https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3" xr:uid="{371BD03B-B8E1-984F-9492-24888A668D04}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>

--- a/static/uploads/Input.xlsx
+++ b/static/uploads/Input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sayanchatterjee/Nextcloud/Work/BlackCoffer/Data-Extraction-and-NLP/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD03B272-C7FE-484E-865D-69715139DB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48551B60-9FD1-4977-A596-F9511A87B413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="18360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="199">
   <si>
     <t>URL_ID</t>
   </si>
@@ -33,59 +33,602 @@
     <t>URL</t>
   </si>
   <si>
-    <t>Nothing Phone 3a</t>
+    <t>Nasher Miles Bag</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Nothing-Phone-White-256GB-Storage/dp/B0DZNP1MN3/ref=sr_1_2?crid=28KDOARO7T5AB&amp;dib=eyJ2IjoiMSJ9.k4LDU1LEvT_DhwCVqJxo_OU04GRP-iBZbw7WF59DYJmmsDs_-8sGogafJ3PWggWVwm7u0ZZuG5mjfDgwZKVERNOyOyEIu_31NNHQhQAQ-nwRHok4G_WSuoTOBDRnIN0DIPNlfun7WovlP6FcHcU60F15THPi_Ce4gvUycMIMDwKjmacKheVUB1mfFPd9PCV1BWqncjQoN-Z7UEjTXpHHCRjktsYNxG3sKJWsw0d9Pgc.1-uK6re4x09tFzUk6VoIDs9mPizwua3TcAAMzzAey6Q&amp;dib_tag=se&amp;keywords=nothing+phone+3a&amp;qid=1748537458&amp;sprefix=nothi,aps,246&amp;sr=8-2</t>
+    <t>https://www.amazon.in/dp/B0DNQV9LKB?th=1&amp;psc=1</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Graphite-Storage/dp/B0DHL7YT5S/ref=sr_1_3?crid=2RBF62FWJ6B00&amp;dib=eyJ2IjoiMSJ9.0BWpZ4ImHW1ZfRnJShi1zt8rS2ZXr8WafZOkgOSNJy6ZEfZ1hwYeKXLo-_RuJx_SP6q3kZ5oHy2xRo6ULiehbeSwws5GCN1AbOWSwhpcPah50e9AED9-5JAS7BMHO8KvX4o_dnRI6mUlkSQwtEdNDqZG81K-wfO7o8zA0-Ox-qKK7OA56W4NHuA6-8FyspcAJjF5yeHBAqIAKEPxDIVNR8aemN5h3BAsdzOTg1zQdXo.qL_kbcmjSDyS6paC8Fc_O02S9a0gPjjgIlZtBHkM4Vs&amp;dib_tag=se&amp;keywords=samsung+s24+fe+5g&amp;qid=1748537484&amp;sprefix=samsun,aps,255&amp;sr=8-3</t>
+    <t>Ugreen Charger</t>
   </si>
   <si>
-    <t>Sony PlayStation®5 Digital Edition (slim) Console Video Game</t>
+    <t>https://www.amazon.in/UGREEN-Charger-RobotGaN-Compatible-MacBook/dp/B0CQ2F185Z/ref=sr_1_3?dib=eyJ2IjoiMSJ9.2RnPQt4UKN2p23clX4O6I2zTzS5p62k2hmIYYU6eASfcu-uZiPrbnyByFR17lsupJh7EhSt2NDpHwFGFoUkrYet-sDf5ofD0YRlkwyID1TuIhLiSXSQ8NFq4LHM3inDIsZLgTCvt2hV0HZXnqvqi4GpzUZ0PZQK0eisUJIQRHq63dyBgXtSkCWV47-oIQOM2fP8jLUwHZeeR0NMG6sLvtv9NTHFd12g22C4lWSpDS5Q.hkbpkCzx6hagsVsoO9Teb7yqVRlXBc3QXVACKywoL40&amp;dib_tag=se&amp;keywords=ugreen+charger&amp;qid=1744190195&amp;sr=8-3</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Sony-PlayStation%C2%AE5-Digital-Edition-slim/dp/B0CY5QW186/ref=sr_1_1?crid=1HILSOLSM638P&amp;dib=eyJ2IjoiMSJ9.pFhgCqcURNHp7Ghh6tpkbnpMS-EPEWOhlo_-YgjavWwZ-kEtUvaKOw7qV5XV-mB3fg-5LyWnXgR1pItjsmQWM-jj2wKAAOgmKNNNtoiqdn78i5oXxajDcrq3lb1p82ZGo7r5uXLGLUcsFEqBDHv5xbIj7uH3EX37_8xmVYmOd6gLcSYuWITMdsVuU2uCbHv4MOIc5w6fI3DojbgPlEWXPI3O3-qh6u4puUatXYP2RMA.IErUARhzqQ1-kuqIXNL4yTseSUcuSl1pT_PM04CPSwo&amp;dib_tag=se&amp;keywords=PS5&amp;qid=1748537909&amp;sprefix=ps5,aps,275&amp;sr=8-1</t>
+    <t>https://www.amazon.in/iPhone-16e-128-Intelligence-Supersized/dp/B0DXQH1DBS/ref=sr_1_3?crid=3F7MCBXZZNOPD&amp;dib=eyJ2IjoiMSJ9.McnHkXYqSX3ITYdLTWgepcOzOthZPc6RN8ugAgMC6Pmn7jv0FaRUj61A-HBqRwVPiHF2XP52K0rxY98fVTcl3fU7RWMiuQ0Nbc3uzF44IsjOI80xnrEBkvryOOdi7EwgXCnL1p9tPZsaajQCVU3IKutJCm4kwGFmaAGMJxnbqAfHIy7LZg2o0P_uQYTQi6nG3OJF7kQk8l8poX5wrjgVe5QKmgCsenMKiEdPgrJvRe8.6e03b7DaPYdK-bW_P9Qn-vi9xMLxNQMU-DYlwivBOWc&amp;dib_tag=se&amp;keywords=iphone+16e&amp;qid=1744190218&amp;sprefix=iphone+16,aps,327&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>Iphone !6e</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Titanium-Storage/dp/B0CS5XW6TN/ref=sr_1_3_mod_primary_new?crid=I66U25A4SGOZ&amp;dib=eyJ2IjoiMSJ9.hv6NA5ualu9lei5y5vIe2MPO39xHMtlvi1ack7oCX2Y1ke_541CeHWU4vyxE_0N4fhv05XPcKPISDYQy3vd1DHG9W-lB61VfKmdRedKrrnAbdEaelupXHddRjTEL_DHCnOxtJdGfoyMv4jCaQ-JMzjKTVYkd7nNOV5IWVSmtQRC71VtvpFmt2MkaIExv2WoETPBdweilDphhPJ5VSMwCTdE_UrN0qR2lc4MKaSJcwB4.jkld_9uvrJaFdH2P99D8DLp8gwi8EY4O0jj875rxP7A&amp;dib_tag=se&amp;keywords=samsung+s24+ultra+5g+mobile&amp;qid=1744197000&amp;sbo=RZvfv//HxDF+O5021pAnSA%3D%3D&amp;sprefix=sa,aps,347&amp;sr=8-3&amp;th=1</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S24 Ultra 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0D7VKMLGD/?_encoding=UTF8&amp;pf_rd_p=9acdf892-017e-42b7-bad2-b4d0ddccbc5e&amp;pf_rd_r=1SAXGECSX0RBZTXF9M45</t>
+  </si>
+  <si>
+    <t>OnePlus Nord 4 5G (Obsidian Midnight, 8GB RAM, 256GB Storage)</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy 45W Charging Adapter</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-Galaxy-Charging-Adapter-Charger/dp/B0DT9N6BC6/?_encoding=UTF8&amp;pd_rd_w=RXGYf&amp;content-id=amzn1.sym.509965a2-791b-4055-b876-943397d37ed3%3Aamzn1.symc.fc11ad14-99c1-406b-aa77-051d0ba1aade&amp;pf_rd_p=509965a2-791b-4055-b876-943397d37ed3&amp;pf_rd_r=DWKTW4E4X5BJFCZH3RVW&amp;pd_rd_wg=1YrvQ&amp;pd_rd_r=827f44b1-c331-4cbf-ae54-827c9408bc7a&amp;ref_=pd_hp_d_atf_ci_mcx_mr_ca_hp_atf_d</t>
+  </si>
+  <si>
+    <t>KZ Castor Pro IEM </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/gp/product/B0DQV99KF1/ref=ewc_pr_img_2?smid=A1647ACVIF71QA&amp;th=1</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S25 5G</t>
+  </si>
+  <si>
+    <t>iPhone 16 Pro Max 256 GB</t>
+  </si>
+  <si>
+    <t>Google Pixel 9 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Google-Pixel-Obsidian-256-RAM/dp/B0DZXTW6PP/ref=sr_1_4?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-4</t>
+  </si>
+  <si>
+    <t>Google Pixel 8a</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Google-Pixel-8a-Obsidian-128/dp/B0DTKDW6XN/ref=sr_1_7?crid=1XUG6D192U96Q&amp;dib=eyJ2IjoiMSJ9.Myl3ECpWftPfFUDgDbpiypqSCMJo6mKHNNLay4S0v_GVs6IINfiZkFA-F3LxEXtdEoVAxYh1eRUgVzAxz6eCg6SsITG0XnteA9mu1s67fuEhm5xQnIO4CogFXJ0BGCFgP5SbZCWvEnr9QK14BDqW3C1f_iwqRQrAlj39z8nOesRRhgAWjZHXLGmJ8QQbhR14TyJLEQkxp1bukCNi2qMrol64pLYxzRP04iINm5dJWzY.3057F7nIydwPfNopSibISCr2U_RFc24_-RJqPiswK3o&amp;dib_tag=se&amp;keywords=google+pixel+phone+9&amp;qid=1748578993&amp;sprefix=goog%2Caps%2C262&amp;sr=8-7</t>
+  </si>
+  <si>
+    <t>iQOO Z10 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/iQOO-Stroage-Snapdragon-Processor-Brightest/dp/B0F2HCGXTB/ref=pd_ci_mcx_pspc_dp_d_2_i_4?pd_rd_w=REU1e&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=F9HNZSR76RRC6VAZ4Y2C&amp;pd_rd_wg=yCnzm&amp;pd_rd_r=daaad224-21b4-4a6a-9aff-98175c4da205&amp;pd_rd_i=B0F2HCGXTB&amp;th=1</t>
+  </si>
+  <si>
+    <t>iQOO Neo 10R 5G </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/iQOO-Snapdragon-Processor-Slimmest-Smartphone/dp/B0DW47XR3X/ref=pd_ci_mcx_pspc_dp_d_2_i_2?pd_rd_w=zBap2&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=AFRZ1JN37C5YSG4858AW&amp;pd_rd_wg=wy8oW&amp;pd_rd_r=82da99e2-58b6-4246-91c1-2d44b8bf87b7&amp;pd_rd_i=B0DW47XR3X&amp;th=1</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy Z Fold6 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-Galaxy-Smartphone-Silver-Storage/dp/B0DH7226XN/ref=sr_1_6?crid=H747DF55NJOJ&amp;dib=eyJ2IjoiMSJ9.61wUedJ5pVCp-MFK_BRxigkS6uwRistnNjecHA3q0AmJPskW40J8akrCGQuMxSCqu4YmgPldxigqy-gZnWlzuW2qISywmQpdGOVXXUyrr8E4059wLE1vrjFq50_C-C3sJQEA3mrExYTFE7ZRWmNWBW_ct68dXonbyH1scy1TiB6YqQMd8fDRNORzJL9hGXJxolX4Ob9ApRQQ79DeUYDCX31Y-2JTvqc35Y1QgB9jl8st-CokI7zuzmjG3ivuOk8rjbeo-QB05eZoGh5RORihd6g2cfnCv4dBDB0hP3cttXc.AkQyZWu0Hconq_oPSOQdwi5olX5D5OeWI5YDKBuDD-0&amp;dib_tag=se&amp;keywords=samsung%2Bfold%2B6%2B5g&amp;qid=1748579132&amp;s=electronics&amp;sprefix=sa%2Celectronics%2C768&amp;sr=1-6&amp;th=1</t>
+  </si>
+  <si>
+    <t>Microsoft New Surface Pro</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0D926JN5N/ref=sspa_dk_detail_5?psc=1&amp;pd_rd_i=B0D926JN5N&amp;pd_rd_w=4KHV6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=E1FY71873BMHPHSN2AW4&amp;pd_rd_wg=2sbSJ&amp;pd_rd_r=5683430e-8263-4dae-9b65-bbbffee54a35&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM</t>
+  </si>
+  <si>
+    <t>Motorola razr 60 Ultra</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HQW3GZ/ref=sr_1_1_sspa?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
   </si>
   <si>
     <t>Samsung Galaxy S25 Ultra</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3</t>
+    <t>https://www.amazon.in/dp/B0DSKNVWK7/ref=sspa_dk_detail_5?pd_rd_i=B0DSKNVWK7&amp;pd_rd_w=5bWOT&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=0ETXZXDS4EWRAA11T15X&amp;pd_rd_wg=A7avg&amp;pd_rd_r=1a644a6d-1c0c-4741-9e61-835460064a2a&amp;s=electronics&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw&amp;th=1</t>
   </si>
   <si>
-    <t>vivo X200 Pro</t>
+    <t>Nothing Phone (3a)</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=sr_1_3?crid=1AMENWB5GO0DY&amp;dib=eyJ2IjoiMSJ9.RW_o5BJcY4Y9WG3FGpJDNY2E7rRbskCmv8HFUmg4n6EViv74acd93v3uxtgVfdbhVM6z7SjbBurkA7pSLQTQfuRw1Ay7dLi6_h0jTqdTYgHGcitGIzlJHHAkTu3a1TOIdZWViQj1lW6yvrg-JBZixt-hLMm9vuDYrLg5fheZ6F4EWzLZD1YnYq4k6STINjwq5959_bqJ_EFSE4T5Ugv2vh86OYG2lhh2qjHrOggU0wQ.v_xGoTBUz1SzSFDlDdfK1T8yuNpLOIlYAz6S-CXzweY&amp;dib_tag=se&amp;keywords=vivo+X200+Pro&amp;qid=1748551943&amp;sprefix=vivo+x200+pro,aps,376&amp;sr=8-3</t>
+    <t>https://www.amazon.in/Nothing-Phone-128GB-Storage-White/dp/B0DZTMFWDB/ref=sr_1_5?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579204&amp;sr=8-5</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Xiaomi-Silver-Chrome-Leica-Quad-Camera/dp/B0DYV4177R/ref=sr_1_3?crid=3BFA6EUJA1KBY&amp;dib=eyJ2IjoiMSJ9.SIwGDtLsGB9zcjOAi-WPna8OoNbV1ZjtaKLSccrPQieStqFpMRS9_hILl-YOrjyfMXIRMOcSLY-HVmOdr2KiKExGLDMLhycRMWdd9sP7EiYC4aFvvYSCLHYE7T1rjAAXrGYdHe2VMIYbRGoYQhEOI4BY90flXzumiCik2orxwlEicoe-vqfG0TQ6XjhUqzw57nCbfg1AqO04Vw3AP6dIO0GJ6_F6kd-NREougY5jYbg.eMEs9lMucx0-o1MQhp-JiQCdGqhUOm9iqfjDohdhhq8&amp;dib_tag=se&amp;keywords=Xiaomi+15+Ultra&amp;qid=1748552015&amp;sprefix=xiaomi+15+ultra,aps,359&amp;sr=8-3</t>
+    <t>Motorola Edge 50 Fusion 5G</t>
   </si>
   <si>
-    <t>Xiaomi 15 Ultra</t>
+    <t>https://www.amazon.in/Motorola-Edge-Fusion-256GB-Storage/dp/B0D4JNVVHH/ref=sr_1_6_mod_primary_new?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sr=8-6&amp;th=1</t>
   </si>
   <si>
-    <t>OnePlus 13</t>
+    <t>realme GT 6T 5G</t>
   </si>
   <si>
-    <t>https://www.amazon.in/OnePlus-13-512GB-Midnight-Ocean/dp/B0DQ8MJYXF/ref=sr_1_3?crid=JVJRW7NMRVIP&amp;dib=eyJ2IjoiMSJ9.ATeYA3KrH9Wb0fbjsbUzvtebcejt3UeUtsz2bSnFdjZYuLZBvPtXKM4JIBLI-ht0IIJ7nHMgy7FCuP-pORHia87pzib1pOvGjv4nb7ZTrqtWuOOJzoukimXDo-l1LC_z6dhpr2BQJEqQz77X7qvpDhekxkm0TO02vMcjqNGLaG23Vzq9-SHIatBT6p63iomGiONoZRyuLO7meIrvwtD2BuKQtDbHVNYz1oy-mCmruqo.uyLDm6GazzMGSo91Vn7lbg0r6sgkbQmiHFaIQl19I84&amp;dib_tag=se&amp;keywords=OnePlus+13&amp;qid=1748552079&amp;sprefix=oneplus+13,aps,457&amp;sr=8-3</t>
+    <t>https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-9&amp;th=1</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Motorola-razr-60-Ultra-Snapdragon%C2%AE/dp/B0F5HVFVKH/ref=sr_1_3?crid=2TMI2QFCK8A8Z&amp;dib=eyJ2IjoiMSJ9.tKCy0Zp_GAMheDynKgHIKQdV9qz4L1fD3DZDQQhhswY8mlPoCpplfNktf4VUGAfGLCxlcOtf_1ZzPnuhWmxKmiRpLE7i6jY1d-DqR0BxBLlvBMfzgRZEirdESJ3UL-mtgttGySVhoXKEppbruoAsAurLddH6JqfCkxounMBnu950XDmY9mShgErmWowuYWbEBe4ylBxByIZceHSy1eFLF4QEEzqJsryemKLK09aXN8E.uk9Yi-AdiOEX1x37cMYYfHi8bLDw3r-OA7cS4Llvon0&amp;dib_tag=se&amp;keywords=Motorola+Razr+60+Ultra&amp;qid=1748552120&amp;sprefix=motorola+razr+60+ultra,aps,529&amp;sr=8-3</t>
+    <t>OnePlus Nord 4 5G </t>
   </si>
   <si>
-    <t>Motorola Razr 60 Ultra</t>
+    <t>https://www.amazon.in/OnePlus-Oasis-Green-256GB-Storage/dp/B0D7VGZS69/ref=sr_1_13?dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579204&amp;sr=8-13&amp;th=1</t>
   </si>
   <si>
-    <t>Samsung S24 FE</t>
+    <t>Tecno Phantom V Fold 2</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Tecno-Phantom-Rippling-Strongest-Segment-5750mAh/dp/B0DMFMGP26?ref_=ast_slp_dp&amp;th=1</t>
+  </si>
+  <si>
+    <t>Vivo X200 Pro 5G </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Titanium-Storage-Additional-Exchange-Offers/dp/B07WDJMX16/ref=pd_ci_mcx_pspc_dp_d_2_i_3?pd_rd_w=S6Z9N&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=SGPZ20XYD9Z855DH79DX&amp;pd_rd_wg=ZtqtS&amp;pd_rd_r=56c17fa8-dc26-455c-a1d0-89527bdb1f77&amp;pd_rd_i=B07WDJMX16&amp;th=1</t>
+  </si>
+  <si>
+    <t>Vivo V50 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/V50-Titanium-Storage-Additional-Exchange/dp/B0DTHTDGH7/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=McAzb&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=TNAJS6HGN2K64V4EXQWC&amp;pd_rd_wg=x0A3e&amp;pd_rd_r=ec7395f2-2a19-4df3-a4bf-467cd54bba52&amp;pd_rd_i=B0DTHTDGH7&amp;th=1</t>
+  </si>
+  <si>
+    <t>Vivo Y300 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Titanium-Silver-Storage-Additional-Exchange/dp/B07WDKLBLZ/ref=srd_d_psims_d_sccl_3_4/258-6142209-0213810?pd_rd_w=sHumC&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=AH74NRK5E4R0JMQ9YKXW&amp;pd_rd_wg=FVloH&amp;pd_rd_r=cf31b8f8-2bcb-462f-b5d0-372f7333cf8d&amp;pd_rd_i=B07WDKLBLZ&amp;th=1</t>
+  </si>
+  <si>
+    <t>Microsoft New Surface Laptop</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Microsoft-New-Surface-Laptop-7th/dp/B0D926W4YN/?_encoding=UTF8&amp;pd_rd_w=1TdJ6&amp;content-id=amzn1.sym.3eb27980-84ee-4cfe-bafb-8634b1863e1c%3Aamzn1.symc.36bd837a-d66d-47d1-8457-ffe9a9f3ddab&amp;pf_rd_p=3eb27980-84ee-4cfe-bafb-8634b1863e1c&amp;pf_rd_r=KHM482DQEKG0FAQM24ZF&amp;pd_rd_wg=7WkzK&amp;pd_rd_r=e13f396a-7510-4d17-a7dc-32d9d44aabf0&amp;ref_=pd_hp_d_btf_ci_mcx_mr_hp_atf_m</t>
+  </si>
+  <si>
+    <t>Lenovo Yoga Slim 7 Intel Core Ultra 7 155H</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0CTMQDLQX/ref=sspa_dk_detail_4?psc=1&amp;pd_rd_i=B0CTMQDLQX&amp;pd_rd_w=86IeU&amp;content-id=amzn1.sym.413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_p=413ef885-ae1b-472f-afa4-d683cda6ad0d&amp;pf_rd_r=X44ASJRS41G0YA96ZSJ3&amp;pd_rd_wg=YNZCM&amp;pd_rd_r=f7457ebd-277d-47b7-ab37-415a2064c6fe&amp;s=computers&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw</t>
+  </si>
+  <si>
+    <t>Apple iPad Pro 13″ (M4)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Apple-iPad-Pro-13%E2%80%B3-Landscape/dp/B0D3J873LP/ref=sr_1_1_sspa?crid=E2N7UN1ZR756&amp;dib=eyJ2IjoiMSJ9.ryvl7KdNIb0IAWsDECGGz1Lpv7AVeXFPCG9nL2u2hH1jlVzBSy-6of4dThVprBSe7pFriHsoGif5s0vdJU6eU3sz5vMlFmX1hSF8WyEndpuwMGRzys16RRiSaGBbx_dcfeNJLyWFNRipJu7HZXuIfenAtEA82v4-bxZm8ATjGP7Zw37MNPhnwN19AoGU9nK7BJ31mGtWpdf0rlWTzKx63l9-aQ66zRnBjK6yFqQOsxoEvI8ylAXQEfWhD9S6-fzk8ywbFkVC5xAiFLCSHQLZdqxSF3iMvU23_QynKFikx3U.UjDRoH9LsisLnn9GEGBnZQNW1qU1dOsdkFh33f66fgY&amp;dib_tag=se&amp;keywords=ipad&amp;qid=1748579721&amp;s=computers&amp;sprefix=ipa%2Ccomputers%2C301&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>Redmi Note 14 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Redmi-Note-14-5G-Dimensity/dp/B0DPFVDFT3/ref=sr_1_3?crid=1PSI4GMX0T3IW&amp;dib=eyJ2IjoiMSJ9.W0mP-4mRHAFSFChkhNzTq330kdGb2A3u4ZQgdLOQy6pY6Mh_SUfqUIQAY4Ap3xJhHz6qzp6KY1CIbw0OrpJvhqFTMOr6Nf2YkqLIFaA3e2FHxvMVsVEf78VpGUvaOhVDYgRw4PHLOul2vNg0ots1Fz10GH4ztE8BOj6F2LC-17l4RDVxrnZuLBzzgAyHS7Uk5pJRj1cR-iiGxtxegHCa_y_XuWsZq_fnBqiGz9T_mSE.eGVmOd6MpRVUCcO08ET0YJltzfavno85ewjLTXb34X0&amp;dib_tag=se&amp;keywords=redmi%2Bnote%2Bphone&amp;qid=1748579813&amp;sprefix=redmi%2Bnote%2Bphone%2Caps%2C271&amp;sr=8-3&amp;th=1</t>
+  </si>
+  <si>
+    <t>OnePlus Nord CE4 Lite 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/OnePlus-Super-Silver-128GB-Storage/dp/B0D5YCYS1G/ref=sr_1_4?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-4&amp;th=1</t>
+  </si>
+  <si>
+    <t>realme NARZO 70 Turbo 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/realme-Segments-Dimensity-Motorsports-Inspired/dp/B0DDTXW9WH/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=wnG2H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=REVXNWXBRG09J9TMKNH4&amp;pd_rd_wg=U1U96&amp;pd_rd_r=45ed424d-bebb-4197-95cf-7c57085fb431&amp;pd_rd_i=B0DDTXW9WH&amp;th=1</t>
+  </si>
+  <si>
+    <t>Apple iPhone 15</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Apple-iPhone-15-128-GB/dp/B0CHX1W1XY/ref=srd_d_psims_d_sccl_3_7/258-6142209-0213810?pd_rd_w=5xRry&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=EDVW8QYE5PKDRKQ23XSY&amp;pd_rd_wg=MJuTs&amp;pd_rd_r=36f69584-50fd-4e16-8d3a-ce379b657030&amp;pd_rd_i=B0CHX1W1XY&amp;th=1</t>
+  </si>
+  <si>
+    <t>HONOR X9b 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Midnight-Ultra-Bounce-Anti-Drop-Display-5800mAh/dp/B0CSDQ434W/ref=sr_1_8?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748579879&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-8</t>
+  </si>
+  <si>
+    <t>HONOR 200 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/6-7-inch-Quad-Curved-Display-AI-Powered-MagicOS/dp/B0D6VJ6FYG/ref=pd_ci_mcx_pspc_dp_d_2_t_1?pd_rd_w=E9EkX&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=RQAM2K1YQBEH3TFVVS39&amp;pd_rd_wg=Zr48l&amp;pd_rd_r=0c9f03f1-6df4-4e80-8d8c-4dbc37296080&amp;pd_rd_i=B0D6VJ6FYG&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/realme-Storage-Flagship-Chipset-Brightest/dp/B0D3J8HYDD/ref=sr_1_9?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.3jRohZrosYYPzcGOjjLqQDP-91O8VE5a-wIeGnZZXiRahuYMynfukpXbICUJa0UCDGZYlagSnXGqJrrDqQgEMROsuKFYhogwuhNvwZ7jhPMKfD4FIjh7bP0SU4qzL0x8ztASiI5lLxxmjmKrFKXabPgYJLSiHDj3bgLT4vFm1rkz4ge_krzEeiI6H5goaA6jykeZMqcFazwZZDYoLu-wFExmabr6tdhHkS_g2meHEGM.cNtWRdVOpk-WkvEpv5VK813F1o0LVO4cAay64-JLStg&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748579879&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-9&amp;th=1</t>
+  </si>
+  <si>
+    <t>Acer Super ZX 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Storage-Display-Ultra-Thin-Dimensity-Processor/dp/B0F4DL4WRB/ref=sr_1_17_sspa?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.SvAv7abmILQkj0mw_Zi71BCAcfEAbz_OohtYwU7NyabGjHj071QN20LucGBJIEps.FJgwiatRdXJrLca9nx4xv5RAX7hU46HGtvYjM09u_H4&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-17-spons&amp;xpid=f4P30bceOuJbj&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGZfbmV4dA&amp;th=1</t>
+  </si>
+  <si>
+    <t>POCO M7 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/POCO-Ocean-Blue-6GB-128GB/dp/B0F135PGDX/ref=sr_1_17?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new+phones&amp;qid=1748580156&amp;sprefix=new+phone%2Caps%2C284&amp;sr=8-17&amp;xpid=f4P30bceOuJbj</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy S25 Edge 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-Smartphone-Precision-Ultra-Sleek-Snapdragon/dp/B0F7LMLR28/ref=sr_1_22_sspa?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-22-spons&amp;xpid=f4P30bceOuJbj&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9tdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>Lava Bold 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Lava-Bold-5G-Dimensity-Resistance/dp/B0F1N1KN2K/ref=sr_1_26?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.oqexx9oZtA23gXVWLYPayjuL2aeCj9y5clvc9bCGtnqmsDs_-8sGogafJ3PWggWVuJYJ56tpBEQP_kVeR-HYUfN27AFAn5Sxe1Dpm4JLmXlxFKmfJtaMtAzNy4o-bD1u_poRNmZ2Wg5mnZJxFGa63UmoEjU_9sjtr_PkNnt-LI6DkAfB2zYnNN1AbHNYVind.4oqHfEbv1sAl3g9cIpIp2Fsg-X8P8ukOnnpa4SAZoEU&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580156&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-26&amp;xpid=f4P30bceOuJbj&amp;th=1</t>
+  </si>
+  <si>
+    <t>Lava Agni 3 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Lava-Agni-Glass-Dimensity-Replacement/dp/B0DGQMDVRV/ref=pd_ci_mcx_pspc_dp_d_2_t_3?pd_rd_w=vOHEI&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=NSXXBGVS65PMASRH43PN&amp;pd_rd_wg=viYGB&amp;pd_rd_r=fd3f4129-7e2b-410e-ae61-0c1e8f4bf4ef&amp;pd_rd_i=B0DGQMDVRV&amp;th=1</t>
+  </si>
+  <si>
+    <t>Infinix Note 50x+ 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Infinix-Enchanted-MediaTek-Dimensity-Expansion/dp/B0F3V2TCLL/ref=pd_ci_mcx_pspc_dp_d_2_t_2?pd_rd_w=I4e1H&amp;content-id=amzn1.sym.b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_p=b5387062-d66f-4264-a2b3-7498b12700ed&amp;pf_rd_r=MY63V7KK31MQQQZESVD6&amp;pd_rd_wg=8dJAy&amp;pd_rd_r=877ba305-e7d9-4d3f-86b8-993add282ee4&amp;pd_rd_i=B0F3V2TCLL</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy M35 5G</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-Daybreak-Storage-Corning-Gorilla/dp/B0D812DY6P/ref=sr_1_34?crid=3GJYJ6IPFOVW0&amp;dib=eyJ2IjoiMSJ9.OfEV2whiq_ABAXeH8Gg7sDgz8wuRTO5b5Ry2fRLtCTl47qwH8Ao3BZGJRkRZtURifBIpfIi0WP6rN59PAY0LqvxQI90aU0BvqCt6OQlE4riWaosru64MOI3igWuz59C77-25ckUUsVtl1lAH-AlTxDClPE8Lq1rAy2eJGAGreCJ5WPDAAKiVarGjnnk8U2Nl.-G5tsWyhDM_n5ubY0BtQ7kjjZmxzqb01h9pMqdeylEc&amp;dib_tag=se&amp;keywords=new%2Bphones&amp;qid=1748580469&amp;sprefix=new%2Bphone%2Caps%2C284&amp;sr=8-34&amp;xpid=f4P30bceOuJbj&amp;th=1</t>
+  </si>
+  <si>
+    <t>Samsung 9 kg, 5 Star,Washing Machine</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-Ecobubble-Inverter-Fully-Automatic-WW90DG6U24ASTL/dp/B0DS681G4K/ref=sr_1_1_sspa?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>G 7 Kg 5 Star Smart Inverter Technology Fully Automatic Top Load Washing Machine</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/LG-Technology-Automatic-T70VBMB1Z-Turbodrum/dp/B0DPHT2HZL/ref=sr_1_4?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-4&amp;th=1</t>
+  </si>
+  <si>
+    <t>Whirlpool 7 kg Magic Clean 5 Star Fully Automatic Top Load Washing Machine</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Whirlpool-MAGIC-CLEAN-7-0-GENX/dp/B0DSBRDRDV/ref=sr_1_8?crid=1F79UY9ZIKFG&amp;dib=eyJ2IjoiMSJ9.NPLt8QIKRCKZhnxbvzTHZn5z7spljYmpto5VAKZ5SDMN41HBKbrj91ufpvv5_9OEcGukUk2KFZFub3QisoW7wMYI02LSg5MvXaKTie9EB-QXXbtqEYvZg_akPSIEetNIvyf5a2y380NMqisGVHyLit8PnazRlE1U1AEfBdvqwETomuBFzjFfsXvNASDKm_gdllIP_vHN2O6g3gQpCAjBITvWz9zTro_yKBEYM_OFuEI.DdZ2tLO-2riy3ytDnmBTr4n7lvlROqe1Gnpbk2aQgvw&amp;dib_tag=se&amp;keywords=washing%2Bmachine&amp;qid=1748580514&amp;sprefix=washing%2Bmachine%2Caps%2C258&amp;sr=8-8&amp;th=1</t>
+  </si>
+  <si>
+    <t>Godrej 472 L 2 Star With AI Tech, 95%+ Food Surface Disinfection with Nano Shield Technology Inverter Frost Free Double Door Regalis Refrigerator</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Godrej-Disinfection-EON-474B-RCI/dp/B0DB63CFRM/ref=sr_1_2_sspa?crid=37P0GGCK5ACZT&amp;dib=eyJ2IjoiMSJ9.TppAajLqXe23_Sosbp2ufvf1D8HP93oZXrx9i0I1gHgdQbY0dp9j9evkWFLa2PX3GjPtU160Bmbu9KF1jxusSJivn-iybZYLDXS8rt8Kob645PG60Pv_sbuub8uKkdggFvOA8ZnlXDF3PBVPeJfmn_YWMPn3F3GPn8GAlpKzRD7Y_Jl5oJkSh7AxJ_a8Fa8O8VNJFtgI9d5YpXv8rMz2g4yB7boUdxgSAmTIg4PLo_4.wwCrmhBPtDA9C4jUJGSo1XjQYr5GmPENroe8g9eo29g&amp;dib_tag=se&amp;keywords=refrigerator&amp;qid=1748580697&amp;sprefix=refrigerator%2B%2Caps%2C269&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>oltas Beko 470 L 2 Star Inverter Frost-Free Double Door Refrigerator</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B081B9RN1C/ref=sspa_dk_detail_3?pd_rd_i=B081B9RN1C&amp;pd_rd_w=NLrAT&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=9C0900TNBPWNT866041X&amp;pd_rd_wg=jlUFi&amp;pd_rd_r=fb73e99a-cc15-4ecd-9461-b95877a94684&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>LG 14 Place Setting Free Standing Dish Washer</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B09THF5XDX/ref=sspa_dk_detail_4?pd_rd_i=B09THF5XDX&amp;pd_rd_w=7c25B&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7MEMS8F80JA2611ZNZ&amp;pd_rd_wg=Qn3DF&amp;pd_rd_r=0623b087-bb73-45e4-a989-2fd91f8c41d6&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>PHILIPS Air Fryer NA352/00 with Rapid Air Technology</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0D4ZCRPKL/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B0D4ZCRPKL&amp;pd_rd_w=0QoxV&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=A2XD4X8YVVSRM2A2W5RH&amp;pd_rd_wg=mNemE&amp;pd_rd_r=e3fd8b1b-708c-4f97-bdd2-59a33f195aa2&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM</t>
+  </si>
+  <si>
+    <t>KENT Digital Air Fryer Oven 12L | 1800W | 360° Rapid Heat Circulation | 10 Preset Menus | Bake, Grill &amp; Roast | Digital Display &amp; Touch Control Panel | Dehydration &amp; Rotisserie Function</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0DGKDWVTZ/ref=sspa_dk_detail_0?pd_rd_i=B0DGKDWVTZ&amp;pd_rd_w=EHGX7&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=HV7R4VQYSC1EF5H7BEC7&amp;pd_rd_wg=YCau9&amp;pd_rd_r=8d3aa661-3d64-4c90-b50f-1925fab1f38a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>Geek AiroCook Zenix 25 Litre Electric Air Fryer Oven, 18 Digital Preset Menus with Rotisserie, Airfry, Bake, Grill, Toast</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0CJMJMBTZ/ref=sspa_dk_detail_6?pd_rd_i=B0CJMJMBTZ&amp;pd_rd_w=dBCxE&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=MCZMCXBRWA9F7BBG1WGK&amp;pd_rd_wg=L7CGB&amp;pd_rd_r=1c9e8f4f-60a1-4877-95fe-4253e053d977&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>Pigeon Healthifry Digital Air Fryer</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Pigeon-Healthifry-Circulation-Technology-Non-Stick/dp/B0B8XNPQPN/ref=srd_d_vsims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=1uMj2&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=YY1XC31NXMQNRPZXVJY8&amp;pd_rd_wg=Bp8bg&amp;pd_rd_r=67ee7bf9-08c3-4261-bb9b-97201df18234&amp;pd_rd_i=B0B8XNPQPN&amp;th=1</t>
+  </si>
+  <si>
+    <t>LG 1 Ton 4 Star DUAL Inverter Split AC</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/LG-Convertible-AntiVirus-Protection-US-Q13JNYE/dp/B0DQQ55C8M/ref=sr_1_3?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-3&amp;th=1</t>
+  </si>
+  <si>
+    <t>Winix Premium 4 Stage Air Purifier,Kills Virus&amp;Bacteria</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B01D8DAYBA/ref=sspa_dk_detail_1?pd_rd_i=B01D8DAYBA&amp;pd_rd_w=azCm6&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7DGGQGMEECRRE4RKC1X5&amp;pd_rd_wg=FNXnv&amp;pd_rd_r=65844888-b77f-43cd-b349-4e4459503458&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>Carrier 1.5 Ton 5 Star Wi-Fi Smart Flexicool Inverter Split AC</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Carrier-Flexicool-Inverter-Convertible-CAI19EE5R35W0/dp/B0DSXJFF5H/ref=sr_1_8?crid=9EZOLWVCJ11V&amp;dib=eyJ2IjoiMSJ9.DZsMnvhEl8fZu71Zt4JUKPb2eLr0Yaz70hPqaRudrMdWD8DgdeijppvCCEWxJnAaNGMT8KpKqgGFwzXIrvs7F4HORIyPJytH1btG94hKsE6iL73pYg0ho55SpbN_MhLeyjB2FgRelsuNA-vhnBQen8AaFesBBvpikbkvQcCL4xqpZP_QSejp7SM36fzSN9ad6Pwq_lYx4ZQHUfRbDRGolq5Rj7lSaLQw-B4Yb1BVS7A.ht9LGmUiEh0NxThPFBG-gVL9UgQcI0p6RtvRf_LPM0s&amp;dib_tag=se&amp;keywords=air%2Bconditioner&amp;qid=1748580977&amp;sprefix=air%2Bconditone%2Caps%2C254&amp;sr=8-8&amp;th=1</t>
+  </si>
+  <si>
+    <t>Daikin 1.5 Ton 3 Star Inverter Split AC</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Daikin-Inverter-Display-Technology-MTKL50U/dp/B0BK1KS6ZD/ref=srd_d_vsims_d_sccl_3_14/258-6142209-0213810?pd_rd_w=QRfaV&amp;content-id=amzn1.sym.7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_p=7ccbe032-5929-4c88-ab39-4923842061df&amp;pf_rd_r=6V8ZS1Q42S3DPSNSZHJK&amp;pd_rd_wg=2kdn2&amp;pd_rd_r=a530f7c0-4de0-4bc4-a7e0-7ba90bb97e65&amp;pd_rd_i=B0BK1KS6ZD&amp;th=1</t>
+  </si>
+  <si>
+    <t>TCL 248 cm (98 inches) 4K Ultra HD Smart QD-Mini LED Google TV 98C755 (Black)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/TCL-inches-QD-Mini-Google-98C755/dp/B0CMDB7D11/ref=sr_1_1_sspa?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>Sony BRAVIA 3 Series 215 cm (85 inches</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Sony-BRAVIA-inches-Google-K-85S30/dp/B0D3DVZ9YD/ref=sr_1_4?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-4&amp;th=1</t>
+  </si>
+  <si>
+    <t>Hisense 215 cm (85 inches) Q7N Series 4K Ultra HD Smart QLED TV 85Q7N</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Hisense-inches-Ultra-Smart-85Q7N/dp/B0D3X8H9PD/ref=sr_1_6?crid=DOQL99XOR382&amp;dib=eyJ2IjoiMSJ9.DOtA-6wibXoqrawhxBzX3_jiCcdwClSM0Z52Es3abeDM0hPc9vrLKIFpZW4W00sgnqoEeuDA3YG3vrcRKjObjNwqzcUVVP3hsrzFSiB60E9Fu1itg8FlxmxjsRmTLzCCiQSiKG6-lMqfJjjP2ZRjtx3uqbQXhC6rL9h_We1iMumXbWn-TLZovjh40nd6dJnGuyrD0mh7SdMVHlxYHmuH2SyMmjlJ--gEo8OBpImE3yA.cTjX33ETO8z647oXAG8Tm17xTJatyO1DqEJaG99c6J4&amp;dib_tag=se&amp;keywords=tv%2B85%2B%2Binch&amp;qid=1748581173&amp;sprefix=tv%2B85%2Caps%2C259&amp;sr=8-6&amp;th=1</t>
+  </si>
+  <si>
+    <t>E GATE Duster 7X 100% Dust Proof Automatic Android Projector</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0CZJ2Z6DS?pd_rd_i=B0CZJ2Z6DS&amp;pf_rd_p=c6080562-3381-4d95-ad87-c0347e4ad274&amp;pf_rd_r=93BXWH59MBXNP919J25A&amp;pd_rd_wg=VeAGI&amp;pd_rd_w=c4tUx&amp;pd_rd_r=da89135f-e94b-471b-8aa0-2a69e1fe36a3&amp;th=1</t>
+  </si>
+  <si>
+    <t>2025 BORSSO Pixel Power | Certified Android 13 Projector</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B07XH4X69F/ref=sspa_dk_detail_3?pd_rd_i=B07XH4X69F&amp;pd_rd_w=hwg2b&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QZRKDWEAEJS35AFT3AJF&amp;pd_rd_wg=g5NJZ&amp;pd_rd_r=6f7c1d7f-e11f-4fab-ad48-ebbe2c35c872&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>Amazon Fire TV Stick 4K </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/All-new-Amazon-streaming-ultra-cinematic-supports/dp/B0CJLMSPXH/ref=pd_sim_d_sccl_4_2/258-6142209-0213810?pd_rd_w=mUp6Z&amp;content-id=amzn1.sym.1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_p=1f02df7f-f362-4e6d-9a92-f270d75713e4&amp;pf_rd_r=447DYHTE3TVM3M25G23X&amp;pd_rd_wg=PyL8C&amp;pd_rd_r=6804b889-b2f4-4e25-be52-5e0adba83ae1&amp;pd_rd_i=B0CJLMSPXH&amp;psc=1</t>
+  </si>
+  <si>
+    <t>Amazon Echo (4th Gen) | Premium sound powered by Dolby and Alexa (Black)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/All-new-Echo/dp/B085FY9NK8/ref=pd_adz_ddpd_wwa_d_sccl_1_5/258-6142209-0213810?pd_rd_w=d1xx8&amp;content-id=amzn1.sym.5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_p=5f46617a-2ec8-444d-a581-a53a486a5183&amp;pf_rd_r=HSTASKGBG6NBD8525F2W&amp;pd_rd_wg=Y5NMd&amp;pd_rd_r=25132703-87f0-455b-9e0c-b200d10f0d87&amp;pd_rd_i=B085FY9NK8&amp;th=1</t>
+  </si>
+  <si>
+    <t>Luminous Inverlast ILTT28060 Battery for Home</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Luminous-ILTT28060-Battery-Blue-Standard/dp/B09KV8JYXH/?_encoding=UTF8&amp;pd_rd_w=eWflc&amp;content-id=amzn1.sym.2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_p=2c8e0a89-b07f-4ef1-a9dc-376996c7def1&amp;pf_rd_r=SMH6G5JSNC5JCBFFVC9W&amp;pd_rd_wg=E3dRj&amp;pd_rd_r=dc570d4e-1862-4b3d-a1db-2d244cb954b6&amp;ref_=pd_hp_d_btf_ls_gwc_pc_en2_&amp;th=1</t>
+  </si>
+  <si>
+    <t>EZVIZ by Hikvision|3k H9C Dual-Lens (5MP+5MP) Pan &amp; Tilt Wi-Fi Camera</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/EZVIZ-Hikvision-Dual-Lens-AI-Powered-Weatherproof/dp/B0D7MM2CF4/ref=srd_d_psims_d_sccl_3_3/258-6142209-0213810?pd_rd_w=Db89u&amp;content-id=amzn1.sym.6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_p=6b3aa144-fd3f-4cac-9ae1-ac2407bcccc2&amp;pf_rd_r=N1EHFX6AMAEFJS2G7PX1&amp;pd_rd_wg=5mLn7&amp;pd_rd_r=68e5a988-d09e-46a7-9dfb-7a0315e7967b&amp;pd_rd_i=B0D7MM2CF4&amp;th=1</t>
+  </si>
+  <si>
+    <t>Imou 3MP Smart CCTV Security WiFi Camera for Home, 360° Coverage, AI Human Detection, Siren Alarm, Night Vision</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/gp/aw/d/B0D7C3QCW3/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=0d29b0c315192cdf5ee5ce3a4a0575f4&amp;hsa_cr_id=7400220020502&amp;sr=1-2-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_1_img&amp;pd_rd_w=Nls3Y&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=RAQVTBS32RNB8YG416TN&amp;pd_rd_wg=uc08r&amp;pd_rd_r=32a129e3-ede1-4707-b014-dc44143585e2&amp;th=1</t>
+  </si>
+  <si>
+    <t>Imou 5MP CCTV Camera for Home Outdoor, 360° Security WiFi Camera</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0D7BYH8J7/ref=sspa_dk_detail_1?pd_rd_i=B0D7BYH8J7&amp;pd_rd_w=rQZ7H&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=99HG7QH0S35CQH1G9GQ8&amp;pd_rd_wg=7XSkl&amp;pd_rd_r=46cf4975-5bf5-48b2-ab4b-932e88166a58&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>Cmf By Nothing Wireless Earbuds (Orange) - In Ear</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Cmf-Nothing-Wireless-Earbuds-Orange/dp/B0CJ8S7XHQ/ref=lp_207352803031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=0YMQQY4J3ZJFKVP3Q10G&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1</t>
+  </si>
+  <si>
+    <t>soundcore By Anker Liberty 4 Nc Wireless Noise Cancelling In Ear Earbud,98.5% Noise Reduction</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0BZV7M23Q/ref=sspa_dk_detail_3?pd_rd_i=B0BZV7M23Q&amp;pd_rd_w=MgzVx&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=89H9EWGPA7G0A4C27JBP&amp;pd_rd_wg=eg98r&amp;pd_rd_r=cba19b3a-bb3b-4716-8f40-7640087e48b0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>JLab JBuds LUX ANC Smart Active Noise Cancelling Headphones</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0CRM4Q1W1/ref=sspa_dk_detail_3?pd_rd_i=B0CRM4Q1W1&amp;pd_rd_w=1ghHG&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=58JSXKPXMP069JPH531F&amp;pd_rd_wg=KUw3L&amp;pd_rd_r=d479f799-61b8-4ae6-b128-e295f09a08e5&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>SHOKZ OpenRun Pro 2 Bone Conduction Sports Headphones</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/gp/aw/d/B0D2HKCMBP/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=7bea835015be4776101946d6a061b704&amp;hsa_cr_id=0&amp;sr=1-1-undefined&amp;ref_=sbx_be_dp_arbies_lsi4d_asin_0_img&amp;pd_rd_w=8lj31&amp;content-id=amzn1.sym.169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_p=169f68c0-01b4-45e0-a0d9-3a54d711fc9b&amp;pf_rd_r=M9P4E3YE9992CFCHNAJK&amp;pd_rd_wg=qS49t&amp;pd_rd_r=def133b0-0093-496c-b816-0cd269600bd2&amp;th=1</t>
+  </si>
+  <si>
+    <t>ZEBRONICS 1100 Watts Powerful Soundbar, 7.2.4 Home Theatre, Wireless (Dual Satellites + Dual Driver Subwoofer)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/ZEBRONICS-Powerful-Satellites-Subwoofer-Radiators/dp/B0DV3R2QM6/ref=sr_1_2_sspa?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>JBL Cinema SB271, Dolby Digital Soundbar with Wireless Subwoofer for Extra Deep Bass, 2.1 Channel Home Theatre</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/JBL-Soundbar-Subwoofer-Bluetooth-Connectivity/dp/B0B6441RNK/ref=sr_1_4?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.CTjeJC5CFc5LjcFR4m2KHTYycDi3GcoLb0DbS1hMLZ41Iv0wgx_Lt3RIIJAlxjaQ_Xn4DMSBza7WZaK7PJuzH2pTql7wxFL1hqPpAY3Yx0sfiMG9VLrscaOTDiqY83x0YOcYz-A2_XeCinyoHfqh3ms3gvI82qQHUmPZ7llpSenUC5jQaXySFwGNYd31otmHR8evPyLd5OfiFlJD4iM9153qmhyINjxOKB0yIZPWJYE8n9niiuwzcEpAk-O4FICHigkWYOy99OZHHpXbFhDDKBqVoW-qBqpb0hvloRaOEOQ.EBLZ1te1y97e10GQlb1UBUs60bxb2ba6oOiOWYFgZmk&amp;dib_tag=se&amp;keywords=home+theater+speaker&amp;qid=1748581854&amp;s=electronics&amp;sprefix=home+theat%2Celectronics%2C298&amp;sr=1-4</t>
+  </si>
+  <si>
+    <t>Sennheiser AMBEO Soundbar Max - 500 Watts Sound Bar for TV with Built in Subwoofer </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Sennheiser-508683-Ambeo-Soundbar-Black/dp/B07ZRTLK8Z/ref=sr_1_1?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-1&amp;th=1</t>
+  </si>
+  <si>
+    <t>Sony HT-A3000 5.1.ch 360 SSM and Dolby Atmos Soundbar Home Theatre System with Wireless subwoofer</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Sony-HT-A3000-Soundbar-subwoofer-Bluetooth/dp/B0DH5217H7/ref=sr_1_7?crid=T227Y28C4JIR&amp;dib=eyJ2IjoiMSJ9.BxP7FbLzrHkiz3c5l03Kcub1WScE0Oz3WnlIIBFEtyoQ7f6nrMfoD3FkxAD9rOJSkv0REa9Vu47xCdmrAy0wp2Ffwp3-RADxzrN6Cpqlp2ZsKWiwm7l4y-8gFQ3o1VHPMj4RbOUM6l5u5BFzVBCgTpLo6h39C-VZJdVIJMB04XxyFrCtpSXz-9t3I26P9o7vptxkSE3DyUNyOuP7nxPckC6sqnIv836jHeZIbI8pmmk.nbXww0Ihse5xLITCF9ZIqok5A64RQO-mgZJ-JnN-IS4&amp;dib_tag=se&amp;keywords=home%2Btheater%2Bspeaker&amp;qid=1748581968&amp;rnid=100766819031&amp;sprefix=home%2Btheat%2Celectronics%2C298&amp;sr=8-7&amp;th=1</t>
+  </si>
+  <si>
+    <t>Fastrack Astor FR2 Pro 1.43" AMOLED Stainless Steel Smart Watch with SpO2, Heart Rate, BT Calling, Adaptive AOD, Functional Crown, AI Voice Assistant – Smartwatch for Stylish Professionals (Black)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Fastrack-Resolution-SingleSync-Assistant-Smartwatch/dp/B0DGGVHMDS/ref=sr_1_3_sspa?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.3fGhX_Nsx9xtFoE8EY00_kOQ08B-nXcef3xgwdRFuxBzfyNScOqUc7tA11LrDgbIa7PrYRZ4DTqlacTFPH1mL8W8epDpzURB8d_LZ33GCqf-h9-oHJKxHra5V0_mB65D8_XzYmJSTjhAYaGKZBxoOwQ0UYdIY52-r9jML4-6cEyVTWVPtmwvEo9EzxpZCXyPDn5Y122prSRzQcYrqz35pvLeeJVh7XkBWiFR40yWeRpQ4mtMj7avq1oTJmqu3FelCrX2_bAnpFH2udY8aNxkd7Zi7Mmo2DKPs3jDhUSk8CI.a59EzJF6-f8yGQWv6I8CQ_kPT1ZKwFq2oCuPy5l-408&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582050&amp;sprefix=watches%2Caps%2C335&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>Fastrack Radiant FX2 2.04" AMOLED Smart Watch with BT Calling, Voice Assistant, Functional Crown, Metal Alloy Case, 100+ Sports Modes, SpO2, AOD – Smartwatch for Men and Women (Black)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0D7MFV54Q/ref=sspa_dk_detail_6?pd_rd_i=B0D7MFV54Q&amp;pd_rd_w=SjkGo&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=FBF4DA2YN33J66SA8WM2&amp;pd_rd_wg=IQIin&amp;pd_rd_r=cfc8b8ba-aa77-498b-bb5b-ec53050a8123&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1</t>
+  </si>
+  <si>
+    <t>Hamilton Khaki Watch, Analog Watch</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Hamilton-Khaki-Watch-Analog/dp/B09HMJ6NXS/ref=sr_1_1?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.vpNmFA-2m3imGj3Ydt2TqINuNKcgVMtDYOgdVnK4nb4tnBUEQQ-Oe-6VQVA_bTxULY4ofb5qWHS1ZPqcktAaWZUXNLOnoeksm6RLzGQLUKMCQuwWfko76r3Lpj61xDtqD96dxMMiakR0qnxTDu9QKKAaYatoR05mz7G0jBqCAMc4h11J1bU3Yy93V5YvGhIkQRDWNFcuJTrlZbc4bZ1OeT7MO-DO8TYnYwKJu-46H_w8SOhk7lqNM8ijJmuW6Pg3eADwzckxlcHRYIIGjALMJaKejnxOuuuhWLx9o81VOHc.cU-Lqskud3Yv4R-CYCga_k_Nuvpq6gnIvCe3Z7RWmew&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582120&amp;sprefix=watches%2Caps%2C335&amp;sr=8-1</t>
+  </si>
+  <si>
+    <t>Atowak Stainless Steel Connected Wrist Watch with Leather Strap Water Resistant, Black Case Material</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Atowak-Stainless-Connected-Resistant-Material/dp/B0CYQ78YBJ/ref=sr_1_2?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.vpNmFA-2m3imGj3Ydt2TqINuNKcgVMtDYOgdVnK4nb4tnBUEQQ-Oe-6VQVA_bTxULY4ofb5qWHS1ZPqcktAaWZUXNLOnoeksm6RLzGQLUKMCQuwWfko76r3Lpj61xDtqD96dxMMiakR0qnxTDu9QKKAaYatoR05mz7G0jBqCAMc4h11J1bU3Yy93V5YvGhIkQRDWNFcuJTrlZbc4bZ1OeT7MO-DO8TYnYwKJu-46H_w8SOhk7lqNM8ijJmuW6Pg3eADwzckxlcHRYIIGjALMJaKejnxOuuuhWLx9o81VOHc.cU-Lqskud3Yv4R-CYCga_k_Nuvpq6gnIvCe3Z7RWmew&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582120&amp;sprefix=watches%2Caps%2C335&amp;sr=8-2</t>
+  </si>
+  <si>
+    <t>Philipp Plein Men's Watch Chronograph Analogue Quartz Nobile Wonder,Gold, gold, bracelet</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Philipp-Plein-Chronograph-Analogue-bracelet/dp/B09SG1S9G9/ref=sr_1_16?crid=1XFTB66S3EQQI&amp;dib=eyJ2IjoiMSJ9.vpNmFA-2m3imGj3Ydt2TqINuNKcgVMtDYOgdVnK4nb4tnBUEQQ-Oe-6VQVA_bTxULY4ofb5qWHS1ZPqcktAaWZUXNLOnoeksm6RLzGQLUKMCQuwWfko76r3Lpj61xDtqD96dxMMiakR0qnxTDu9QKKAaYatoR05mz7G0jBqCAMc4h11J1bU3Yy93V5YvGhIkQRDWNFcuJTrlZbc4bZ1OeT7MO-DO8TYnYwKJu-46H_w8SOhk7lqNM8ijJmuW6Pg3eADwzckxlcHRYIIGjALMJaKejnxOuuuhWLx9o81VOHc.cU-Lqskud3Yv4R-CYCga_k_Nuvpq6gnIvCe3Z7RWmew&amp;dib_tag=se&amp;keywords=watches&amp;qid=1748582120&amp;sprefix=watches%2Caps%2C335&amp;sr=8-16</t>
+  </si>
+  <si>
+    <t>FEICE Watches for Men Automatic Skeleton Watch Waterproof Mineral Glass Japanese Movement Supercar Wristwatch Anti Shock Business Tourbillon FM666</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0C7C5L58J/ref=sspa_dk_detail_6?psc=1&amp;pd_rd_i=B0C7C5L58J&amp;pd_rd_w=N9YUn&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=7W8D6Z0AK1Q15AQ2CN9T&amp;pd_rd_wg=qY8oG&amp;pd_rd_r=01906309-7f6e-4c0f-9a79-60371759ba4a&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM</t>
+  </si>
+  <si>
+    <t>FEICE Men's Watch Wristwatches Chronograph Sport Watch Japanese Quartz Analog-Digital Waterproof Watches FK038</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0CZ77RYDH/ref=emc_bcc_2_i</t>
+  </si>
+  <si>
+    <t>FEICE Wathes for Men Digital LED Analog Quartz Wristwatch Business Men’s Watch Multifunction Square Chronograph 24H Calendar Stainless Steel Band Waterproof Unique FK814</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0D11KW58G/ref=emc_bcc_2_i?th=1</t>
+  </si>
+  <si>
+    <t>Casio G-Shock MTG-B2000YST-1ADR Bluetooth Analog Black Dial Men (G1645)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Casio-G-Shock-MTG-B2000YST-1ADR-Bluetooth-G1645/dp/B0DYF479TH/ref=sr_1_1?crid=19SIHD8E9GDM6&amp;dib=eyJ2IjoiMSJ9.vjQaCeiO6Z_GdhBHU3kAD6VsG0xUjMEMDtRH7wCJcq75msubketXWyft0KahEhz8z8n1UvU6AsvmbVV843xBJ53HlGPmcBZxZfQRuVglBfmnn2-rSO8zFRCG7fvoAyoMmdTZSgigqXWnzjjvpvXD60rbydfho5pd5az8rryhVEiv9o3vGrvHdX3Dq0zO25-bo3o-CiiLEstvwhv1caWQiEQeOvSdZAbHBcLd-jiFc1zg2OybhNhB4q_Ji8vTsAcdgEr4AhE2AL-MteWygbgy7FIjCrpqgSlFhQZ9PPPlBVs.XUloc_Dx8zn8EsD3a8uJN84pDvX0iL-OkXe94sJYL8E&amp;dib_tag=se&amp;keywords=casio&amp;nsdOptOutParam=true&amp;qid=1748582355&amp;s=watches&amp;sprefix=casio%2Cwatches%2C277&amp;sr=1-1</t>
+  </si>
+  <si>
+    <t>Casio G-Shock GPR-H1000-9DR Digital Dial Yellow Bio-Based Resin Band Men's Watch Mud Resistant Barometer Altimeter G1530</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Casio-GPR-H1000-9DR-Bio-Based-Resistant-Barometer/dp/B0CY24PZ9R/ref=sr_1_6?crid=19SIHD8E9GDM6&amp;dib=eyJ2IjoiMSJ9.vjQaCeiO6Z_GdhBHU3kAD6VsG0xUjMEMDtRH7wCJcq75msubketXWyft0KahEhz8z8n1UvU6AsvmbVV843xBJ53HlGPmcBZxZfQRuVglBfmnn2-rSO8zFRCG7fvoAyoMmdTZSgigqXWnzjjvpvXD60rbydfho5pd5az8rryhVEiv9o3vGrvHdX3Dq0zO25-bo3o-CiiLEstvwhv1caWQiEQeOvSdZAbHBcLd-jiFc1zg2OybhNhB4q_Ji8vTsAcdgEr4AhE2AL-MteWygbgy7FIjCrpqgSlFhQZ9PPPlBVs.XUloc_Dx8zn8EsD3a8uJN84pDvX0iL-OkXe94sJYL8E&amp;dib_tag=se&amp;keywords=casio&amp;nsdOptOutParam=true&amp;qid=1748582355&amp;s=watches&amp;sprefix=casio%2Cwatches%2C277&amp;sr=1-6</t>
+  </si>
+  <si>
+    <t>Casio Edifice ECB-900DB-1BDR Bluetooth Analog-Digital Black Dial Men Watch Silver Metal Strap (EX500)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Casio-Analog-Digital-Black-Watch-ECB-900DB-1BDR-EX500/dp/B07RJZWVCV/ref=sr_1_3_sspa?crid=2BKCQK6KDJFJ2&amp;dib=eyJ2IjoiMSJ9.AZV7yuuBFMvOQOyJWTbiXATItoQ2Tdu8c8cdcg8PhHU8n0C65Dg4OAAxFcTOgDiS79gXBoSOqbNYWyrU3kS0syI8SgyHrJ3mRImBwLKWrKa_ql6tPucky7fZfDG_7o8ryZQH897ZVK7B7oHSdpMtbLJLgkwsbU1R0YdREZ9YI8MmyemPWXcFwI1pQe9FgQgrKIp80vXMjTXPqsrqHKCaxMUZIPw62FNgqYUfnayMlkI79EpJEHxBEYRAWI_nsG-5888L4BpvETimzpwJ8ZDRSyZriyWUWhsPb5HaQ6XbcbA.mEjl-zsxtF-NftbJYfvch9fJ4CFLI-QGT_LM5I3lHEs&amp;dib_tag=se&amp;keywords=casio+edifice+watch&amp;qid=1748582550&amp;s=watches&amp;sprefix=casio+edif%2Cwatches%2C254&amp;sr=1-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>Casio Edifice ECB-900MDC-1ADR Gray Analog-Digital Dial Gray Ion Plated Stainless Steel Band Men's Watch Smartphone Link World Time ED527</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Casio-Analog-Digital-Gray-Dial-Watch-ECB-900MDC-1ADR/dp/B09P6LL74N/ref=sr_1_4_sspa?crid=2BKCQK6KDJFJ2&amp;dib=eyJ2IjoiMSJ9.AZV7yuuBFMvOQOyJWTbiXATItoQ2Tdu8c8cdcg8PhHU8n0C65Dg4OAAxFcTOgDiS79gXBoSOqbNYWyrU3kS0syI8SgyHrJ3mRImBwLKWrKa_ql6tPucky7fZfDG_7o8ryZQH897ZVK7B7oHSdpMtbLJLgkwsbU1R0YdREZ9YI8MmyemPWXcFwI1pQe9FgQgrKIp80vXMjTXPqsrqHKCaxMUZIPw62FNgqYUfnayMlkI79EpJEHxBEYRAWI_nsG-5888L4BpvETimzpwJ8ZDRSyZriyWUWhsPb5HaQ6XbcbA.mEjl-zsxtF-NftbJYfvch9fJ4CFLI-QGT_LM5I3lHEs&amp;dib_tag=se&amp;keywords=casio+edifice+watch&amp;qid=1748582550&amp;s=watches&amp;sprefix=casio+edif%2Cwatches%2C254&amp;sr=1-4-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>Samsung 27-Inch(68.5cm) FHD, 1800R Curved 1,920 X 1,080 LED Monitor, VA Panel, Slim Design, AMD Freesync, Flicker Free, HDMI, Audio Port (LC27R500FHWXXL, Dark Blue Gray)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-3-Sided-Bezel-Less-Monitor-LC27R500FHWXXL/dp/B09C2JSMFB/ref=sr_1_4?crid=1MMAQA7CCUBGJ&amp;dib=eyJ2IjoiMSJ9.DHFaumRA9KiatebKt7mDhZF0xiINoGCcue7b2f0JM714dSYGqC7QECYETzoNtlcKbuC-Ut9LxxXTjVtzLthCV5JPOsi4Nsw-Gop84reUQzF1yOfeu7q-j6Owoip_6mtQjU_Nac_790FsSMx8YJ41x50QNWGzMemWB4k_SkFVEZmOBEfgc24Et7xP5CkKMerD1c2C6qP-yB1xqecViqbnboPdXcw0OkGEbdx-At_yCyo.hcVVOcdEdXoh8pTGUaO2lsZy6V-60PMvAwPYYzwfNlM&amp;dib_tag=se&amp;keywords=monitor&amp;qid=1748582654&amp;sprefix=monit%2Caps%2C255&amp;sr=8-4</t>
+  </si>
+  <si>
+    <t>Apple Pro Display XDR (32-inch with Retina 6K Display, Nano-Texture Glass)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Apple-Display-32-inch-Retina-Nano-Texture/dp/B082PRF461/ref=sr_1_2?crid=1MMAQA7CCUBGJ&amp;dib=eyJ2IjoiMSJ9.YCNB9gF742o9MHE3VAjCPaqiCLDdlQXnvL3dF1KXwDVtSINMZgp0iYgpBierQaS2ScvUZTVqELOvOSSEw0uqt640VCzzs4iSMplN-Tfe2a7Ebp4Q6kMYmwqq-n8S7EHKeoNgPxOiecE9Q6PxAzCOT6yLADrpp-jg8kw6TtUOXhOqmbmbcOPebpObOXAEdf0dzXOtY4P2B3YvtYQJvfie2mNVNuKUxI5x9RbbwD6QOp8.nroK49RnqM2Pb-ct-u7SjnQwIGWFIyK4bXAzkqYL64w&amp;dib_tag=se&amp;keywords=monitor&amp;qid=1748582700&amp;sprefix=monit%2Caps%2C255&amp;sr=8-2</t>
+  </si>
+  <si>
+    <t>Samsung 55-inch(138 cm) Odyssey ARK 2nd Gen 4K UHD</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Samsung-55-inch-Bluetooth-FreeSync-LS55CG97WNWXXL/dp/B0DM5XLKT9/ref=sr_1_4?crid=1MMAQA7CCUBGJ&amp;dib=eyJ2IjoiMSJ9.YCNB9gF742o9MHE3VAjCPaqiCLDdlQXnvL3dF1KXwDVtSINMZgp0iYgpBierQaS2ScvUZTVqELOvOSSEw0uqt640VCzzs4iSMplN-Tfe2a7Ebp4Q6kMYmwqq-n8S7EHKeoNgPxOiecE9Q6PxAzCOT6yLADrpp-jg8kw6TtUOXhOqmbmbcOPebpObOXAEdf0dzXOtY4P2B3YvtYQJvfie2mNVNuKUxI5x9RbbwD6QOp8.nroK49RnqM2Pb-ct-u7SjnQwIGWFIyK4bXAzkqYL64w&amp;dib_tag=se&amp;keywords=monitor&amp;qid=1748582700&amp;sprefix=monit%2Caps%2C255&amp;sr=8-4</t>
+  </si>
+  <si>
+    <t>ASUS ROG Strix G22CH 2024, 20 Crore, Intel® Core™ i7-14700F 14th Gen, Gaming Desktop (16GB/1TB SSD/12GB NVIDIA GeForce RTX 4070</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/ASUS-i7-14700F-Desktop-Graphics-G22CH-71470F004WS/dp/B0CV17FR6N/ref=sr_1_1_sspa?crid=1EBFTQ30TU4P4&amp;dib=eyJ2IjoiMSJ9.jmmY2d_92_UcWB9kskAI228qs4X9btmvHdaR531YptOS6_pfWQM0j2Zy7TEH7DrWlF0iBDQIH2dSD4gbXlg4MEj79kEDwrJ9xJ3OUpvuBwIW0vTjFFIP_aN0rMDx_NG5kJmrIw9Vz30L6bbJ1UuMlEGRQfEDG5rsbfmyAjNZ7wLTSn1KhHGfzE3Oq7SvMJvjZ1opQEfSerDy_93XulGsXknTCsBspsJmRqODJg7jgYQ.77lrCBqVnmDZQ-x9f9KzLynP8vsKP3-SVNXlksl1Mak&amp;dib_tag=se&amp;keywords=asus+cpu&amp;qid=1748583031&amp;sprefix=asus+c%2Caps%2C296&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>ASUS TUF Dash Intel Windows 10 15 FX516PM-AZ154T</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/ASUS-TUF-Dash-15-FX516PM-AZ154T/dp/B094X4BD9Q/ref=sr_1_4?crid=1EBFTQ30TU4P4&amp;dib=eyJ2IjoiMSJ9.jmmY2d_92_UcWB9kskAI228qs4X9btmvHdaR531YptOS6_pfWQM0j2Zy7TEH7DrWlF0iBDQIH2dSD4gbXlg4MEj79kEDwrJ9xJ3OUpvuBwIW0vTjFFIP_aN0rMDx_NG5kJmrIw9Vz30L6bbJ1UuMlEGRQfEDG5rsbfmyAjNZ7wLTSn1KhHGfzE3Oq7SvMJvjZ1opQEfSerDy_93XulGsXknTCsBspsJmRqODJg7jgYQ.77lrCBqVnmDZQ-x9f9KzLynP8vsKP3-SVNXlksl1Mak&amp;dib_tag=se&amp;keywords=asus+cpu&amp;qid=1748583031&amp;sprefix=asus+c%2Caps%2C296&amp;sr=8-4</t>
+  </si>
+  <si>
+    <t>MSI Thin 15, Intel Core i7-12650H, 40CM FHD 144Hz Gaming Laptop(16GB/1TB NVMe SSD/Windows 11 Home/NVIDIA GeForce RTX 2050,GDDR6 4GB /Cosmos Gray/1.86Kg), B12UCX-1693IN</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/MSI-i7-12650H-Windows-GeForce-B12UCX-1693IN/dp/B0CV8RGCPH/ref=sr_1_2_sspa?crid=2AD5O668Y3IQ4&amp;dib=eyJ2IjoiMSJ9.F1gBVvIhkKMrO4zuJq8yoqEtY2QmM9yx7UoJFPs9gF3R_2HjmJacYY075oa7X2lr-R16OOE__3RryB2ETGn0vdl0ya8Uc-zSYNTSNyX4OvLxvz6hlIeZt7DQ6H6eWBbjmcLQJTVQOMNXyxM5L-OnDMrYWrOpZ3yDnvvUm4Mk0b9MRuPHDXJtyhrY9pNx8wspfbArWep_unuSYnPCyLMFg8HgxG6cd54ML0nNf36q3ZI.GmP9Y84Q0bN9R2ogbkMaiD0m5KUet-QqOFYgfecCmcM&amp;dib_tag=se&amp;keywords=msi&amp;qid=1748583269&amp;sprefix=msi%2Caps%2C430&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>Apple 2025 MacBook Air (13-inch, Apple M4 chip with 10-core CPU and 8-core GPU, 16GB Unified Memory, 256GB) - Silver</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Apple-MacBook-13-inch-10-core-Unified/dp/B0DZDX3JF4/ref=sr_1_1_sspa?crid=F3T2770V5XLZ&amp;dib=eyJ2IjoiMSJ9.gJr6A0i2Iyyy64nmx7IkquPxcAuSJKM-mlIjorYsao-M40iRKZ3tuZg46uaqkKRpJ0IvoefQ3SeaUsekKxP7ZN2T5GAIsIiCSalUpviVqZoti_-UfUOOqkJrEM9zrAzTy2RORhAnIrLw6aTcIu0PkoLbH9oPsVre41jLwIpYltrbA98QegsOfmuPnDLc4yvKrggYGP7cJb7FVdNQW8B6Mfey0CGqUyw6FsPI7PYM5NM.yGwJTrq9oYh7oHE8GpauMh3Xm4CFg5-Fcmfh43sAK9c&amp;dib_tag=se&amp;keywords=macbook%2Bair%2Bm4&amp;qid=1748583302&amp;sprefix=ma%2Caps%2C263&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>OnePlus Bullets Z2 Bluetooth Wireless in Ear Earphones with Mic, Bombastic Bass, 10 Mins Charge - 20 Hrs Music, 30 Hrs Battery Life (Acoustic Red)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Oneplus-Bluetooth-Wireless-Earphones-Bombastic/dp/B0B3MNYGTW/ref=pd_vtp_strm_d_sccl_3_4/258-6142209-0213810?pd_rd_w=wCYA3&amp;content-id=amzn1.sym.54180577-20e1-4d93-8e42-2e44261ca64d&amp;pf_rd_p=54180577-20e1-4d93-8e42-2e44261ca64d&amp;pf_rd_r=D9T5MRDJSSZVJM8M81DY&amp;pd_rd_wg=nKgUg&amp;pd_rd_r=61aa87e9-4b4d-4d62-b6b4-a40109049330&amp;pd_rd_i=B0B3MNYGTW&amp;th=1</t>
+  </si>
+  <si>
+    <t>Sony Alpha ZV-E10L 24.2 Mega Pixel Interchangeable-Lens Mirrorless vlog Camera with 16-50 mm Lens, Made for Creators | APS-C Sensor | Advanced Autofocus | Clear Audio &amp; 4K Movie Recording - Black</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Sony-ZV-E10L-Interchangeable-Lens-Mirrorless-Autofocus/dp/B09F9Q7287/ref=lp_4368643031_1_1?pf_rd_p=9e034799-55e2-4ab2-b0d0-eb42f95b2d05&amp;pf_rd_r=14B50W9VRW7C1V2NRP38&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;th=1</t>
+  </si>
+  <si>
+    <t>Fujifilm X-H2S 26MP APS-C X-Trans Stacked Sensor|IBIS System|Wedding Camera|Cinematic Camera|Flagship Mirrorless Hybrid Camera|Touchtracking|4K Upto 120fps|6.2K ProRes|F-Log2|for Professionals</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/dp/B0B2F5VHLM/ref=sspa_dk_detail_1?psc=1&amp;pd_rd_i=B0B2F5VHLM&amp;pd_rd_w=rRI4h&amp;content-id=amzn1.sym.9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_p=9f1cb690-f0b7-44de-b6ff-1bad1e37d3f0&amp;pf_rd_r=QP6GXAEVQ599WZPK6CJH&amp;pd_rd_wg=PXBFb&amp;pd_rd_r=374705f7-62e1-43c3-9d70-6b6328d1334d&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM</t>
+  </si>
+  <si>
+    <t>Canon EOS R8 Full-Frame 24.2 MP Mirrorless Camera Body | 4K Full HD Video Recording | (Black)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Canon-Full-Frame-Mirrorless-Camera-Processor/dp/B0BYHHMFY6/ref=sr_1_1?dib=eyJ2IjoiMSJ9.hyHeDkFsrb4AkWpFOZuHlIbka3EI-QIU6_VvMJ2kOiZQ3w-ZGji6x8sGBJs-XZEiZ5BIy4h7i9vG36gNtxG0V-bfkujVpaA4IU-O5E7nuJJKeBf5NIIPGKmyIFmw2AThwdB7a3F6MznoqxOvB16KUJKeeuXYzmdklyOuqdyUCh8BWhfGOXgVxfuAICvVM_LzFQVeSKiEjBJiVh96jfxxWmjEXylpuW_7CzPnZcfiv1uaB2uKEFsmG7U203J9IUEuWiBtk64f2UhFIryINFRHF8Tc0E-oexLW8FJ3OHzv0jc.XcDcSdSROAbW5Xc0YrVGzW8-1wg2HjLMEa0uL3rlWfQ&amp;dib_tag=se&amp;keywords=canon+camera&amp;qid=1748583453&amp;s=electronics&amp;sr=1-1</t>
+  </si>
+  <si>
+    <t>Apple 2024 MacBook Air 13″ Laptop with M3 chip: 34.46 cm (13.6″) Liquid Retina Display, 16GB Unified Memory, 512GB SSD Storage, Backlit Keyboard, 1080p FaceTime HD Camera, Touch ID- Starlight</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Apple-2024-MacBook-Laptop-chip/dp/B0CX23FSQL/ref=sr_1_3?crid=3J4TG6DY67NPE&amp;dib=eyJ2IjoiMSJ9.v2jUy0wPS4uZqXcjxd2j4Ff-KsWFKKBAt1nPRIuFG43nstP2IhE-B7i6KOyh-i3lZ2y-8PhkZm5nX_74ZRXDavEpMGugvNirKsRDQk5gr1_kU85g-tYfi369uVvQ6WKcTYyNax6e-lQPYu-W3LYQjomVUtdHFWNCuRtcrJyzxjZ5gL22xLKhNvpmSV-Om3uYdLAn97pdPpBxuyKejN-Grmic5X88FQXaAmP9TUm6zbE.uhF65HnJVwEkXWZrMNfJEcjjQQVGRrt_gjS8KAQvxyc&amp;dib_tag=se&amp;keywords=laptop&amp;qid=1748583563&amp;sprefix=laptop%2Caps%2C294&amp;sr=8-3&amp;th=1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,6 +697,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FF0F1111"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -205,9 +754,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -219,7 +768,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -437,14 +989,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z932"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="52.1640625" customWidth="1"/>
-    <col min="2" max="2" width="122.5" customWidth="1"/>
+    <col min="1" max="1" width="83.21875" customWidth="1"/>
+    <col min="2" max="2" width="122.44140625" customWidth="1"/>
     <col min="3" max="26" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -476,12 +1028,12 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>8</v>
+      <c r="B2" s="5" t="s">
+        <v>3</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -508,12 +1060,12 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>10</v>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -540,12 +1092,12 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -572,12 +1124,12 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -604,12 +1156,12 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -636,12 +1188,12 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>2</v>
+    <row r="7" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
@@ -668,12 +1220,12 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>17</v>
+    <row r="8" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
@@ -700,12 +1252,12 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>5</v>
+    <row r="9" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>6</v>
+      <c r="B9" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
@@ -732,9 +1284,13 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
+    <row r="10" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>20</v>
+      </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -760,9 +1316,13 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
+    <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -788,9 +1348,13 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
+    <row r="12" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>23</v>
+      </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -816,9 +1380,13 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
+    <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -844,9 +1412,13 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
+    <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -872,9 +1444,13 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
+    <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -900,9 +1476,13 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
+    <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -928,9 +1508,13 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
+    <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>33</v>
+      </c>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -956,9 +1540,13 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
+    <row r="18" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>35</v>
+      </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -984,9 +1572,13 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
+    <row r="19" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>37</v>
+      </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1012,9 +1604,13 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
+    <row r="20" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1040,9 +1636,13 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
+    <row r="21" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1068,9 +1668,13 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
+    <row r="22" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>43</v>
+      </c>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1096,9 +1700,13 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
+    <row r="23" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1124,9 +1732,13 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
+    <row r="24" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1152,9 +1764,13 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
+    <row r="25" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1180,9 +1796,13 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
+    <row r="26" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>51</v>
+      </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1208,9 +1828,13 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4"/>
-      <c r="B27" s="5"/>
+    <row r="27" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>53</v>
+      </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1236,9 +1860,13 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
+    <row r="28" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1264,9 +1892,13 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="5"/>
+    <row r="29" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1292,9 +1924,13 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4"/>
-      <c r="B30" s="6"/>
+    <row r="30" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1320,9 +1956,13 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="4"/>
-      <c r="B31" s="7"/>
+    <row r="31" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>61</v>
+      </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1348,9 +1988,13 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4"/>
-      <c r="B32" s="8"/>
+    <row r="32" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>63</v>
+      </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1376,9 +2020,13 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="4"/>
-      <c r="B33" s="8"/>
+    <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>65</v>
+      </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1404,9 +2052,13 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4"/>
-      <c r="B34" s="8"/>
+    <row r="34" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>67</v>
+      </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1432,9 +2084,13 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4"/>
-      <c r="B35" s="8"/>
+    <row r="35" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1460,9 +2116,13 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="4"/>
-      <c r="B36" s="8"/>
+    <row r="36" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -1488,9 +2148,13 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="8"/>
+    <row r="37" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -1516,9 +2180,13 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="4"/>
-      <c r="B38" s="8"/>
+    <row r="38" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>74</v>
+      </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -1544,9 +2212,13 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="4"/>
-      <c r="B39" s="8"/>
+    <row r="39" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -1572,9 +2244,13 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="4"/>
-      <c r="B40" s="8"/>
+    <row r="40" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>78</v>
+      </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1600,9 +2276,13 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="8"/>
+    <row r="41" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>80</v>
+      </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -1628,9 +2308,13 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="4"/>
-      <c r="B42" s="8"/>
+    <row r="42" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -1656,9 +2340,13 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="4"/>
-      <c r="B43" s="8"/>
+    <row r="43" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>84</v>
+      </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -1684,9 +2372,13 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="4"/>
-      <c r="B44" s="8"/>
+    <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>86</v>
+      </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -1712,9 +2404,13 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="4"/>
-      <c r="B45" s="8"/>
+    <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -1740,9 +2436,13 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="4"/>
-      <c r="B46" s="6"/>
+    <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>90</v>
+      </c>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -1768,9 +2468,13 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="4"/>
-      <c r="B47" s="8"/>
+    <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -1796,9 +2500,13 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="4"/>
-      <c r="B48" s="8"/>
+    <row r="48" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>94</v>
+      </c>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -1824,9 +2532,13 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="4"/>
-      <c r="B49" s="8"/>
+    <row r="49" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>96</v>
+      </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -1852,9 +2564,13 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="4"/>
-      <c r="B50" s="8"/>
+    <row r="50" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -1880,9 +2596,13 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="4"/>
-      <c r="B51" s="8"/>
+    <row r="51" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>100</v>
+      </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -1908,9 +2628,13 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="4"/>
-      <c r="B52" s="8"/>
+    <row r="52" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>102</v>
+      </c>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -1936,9 +2660,13 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="4"/>
-      <c r="B53" s="8"/>
+    <row r="53" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>104</v>
+      </c>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -1964,9 +2692,13 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="4"/>
-      <c r="B54" s="8"/>
+    <row r="54" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>106</v>
+      </c>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -1992,9 +2724,13 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="4"/>
-      <c r="B55" s="8"/>
+    <row r="55" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>108</v>
+      </c>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -2020,9 +2756,13 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="4"/>
-      <c r="B56" s="8"/>
+    <row r="56" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>110</v>
+      </c>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -2048,9 +2788,13 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4"/>
-      <c r="B57" s="8"/>
+    <row r="57" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>112</v>
+      </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -2076,9 +2820,13 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4"/>
-      <c r="B58" s="8"/>
+    <row r="58" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>114</v>
+      </c>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -2104,9 +2852,13 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4"/>
-      <c r="B59" s="8"/>
+    <row r="59" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>116</v>
+      </c>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -2132,9 +2884,13 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4"/>
-      <c r="B60" s="8"/>
+    <row r="60" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>118</v>
+      </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2160,9 +2916,13 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4"/>
-      <c r="B61" s="8"/>
+    <row r="61" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>120</v>
+      </c>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -2188,9 +2948,13 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4"/>
-      <c r="B62" s="8"/>
+    <row r="62" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>122</v>
+      </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -2216,9 +2980,13 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4"/>
-      <c r="B63" s="8"/>
+    <row r="63" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>124</v>
+      </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -2244,9 +3012,13 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4"/>
-      <c r="B64" s="8"/>
+    <row r="64" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>126</v>
+      </c>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -2272,9 +3044,13 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4"/>
-      <c r="B65" s="8"/>
+    <row r="65" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>128</v>
+      </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -2300,9 +3076,13 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4"/>
-      <c r="B66" s="8"/>
+    <row r="66" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>130</v>
+      </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -2328,9 +3108,13 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4"/>
-      <c r="B67" s="8"/>
+    <row r="67" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>132</v>
+      </c>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -2356,9 +3140,13 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4"/>
-      <c r="B68" s="8"/>
+    <row r="68" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>134</v>
+      </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -2384,9 +3172,13 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4"/>
-      <c r="B69" s="8"/>
+    <row r="69" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -2412,9 +3204,13 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4"/>
-      <c r="B70" s="8"/>
+    <row r="70" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>138</v>
+      </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -2440,9 +3236,13 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4"/>
-      <c r="B71" s="8"/>
+    <row r="71" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>140</v>
+      </c>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -2468,9 +3268,13 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="4"/>
-      <c r="B72" s="8"/>
+    <row r="72" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>142</v>
+      </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -2496,9 +3300,13 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="4"/>
-      <c r="B73" s="8"/>
+    <row r="73" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>144</v>
+      </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -2524,9 +3332,13 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4"/>
-      <c r="B74" s="8"/>
+    <row r="74" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>146</v>
+      </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -2552,9 +3364,13 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="4"/>
-      <c r="B75" s="8"/>
+    <row r="75" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>148</v>
+      </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -2580,9 +3396,13 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="4"/>
-      <c r="B76" s="8"/>
+    <row r="76" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>150</v>
+      </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -2608,9 +3428,13 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="4"/>
-      <c r="B77" s="8"/>
+    <row r="77" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>152</v>
+      </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -2636,9 +3460,13 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="4"/>
-      <c r="B78" s="9"/>
+    <row r="78" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>154</v>
+      </c>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -2664,9 +3492,13 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="4"/>
-      <c r="B79" s="9"/>
+    <row r="79" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>156</v>
+      </c>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -2692,9 +3524,13 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="4"/>
-      <c r="B80" s="9"/>
+    <row r="80" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>158</v>
+      </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -2720,9 +3556,13 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="4"/>
-      <c r="B81" s="9"/>
+    <row r="81" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>160</v>
+      </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -2748,9 +3588,13 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="9"/>
+    <row r="82" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>162</v>
+      </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -2776,9 +3620,13 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="4"/>
-      <c r="B83" s="9"/>
+    <row r="83" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>164</v>
+      </c>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -2804,9 +3652,13 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="4"/>
-      <c r="B84" s="9"/>
+    <row r="84" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>166</v>
+      </c>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -2832,9 +3684,13 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="4"/>
-      <c r="B85" s="9"/>
+    <row r="85" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>168</v>
+      </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -2860,9 +3716,13 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="4"/>
-      <c r="B86" s="9"/>
+    <row r="86" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>170</v>
+      </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -2888,9 +3748,13 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="4"/>
-      <c r="B87" s="9"/>
+    <row r="87" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>172</v>
+      </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -2916,9 +3780,13 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="4"/>
-      <c r="B88" s="9"/>
+    <row r="88" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>174</v>
+      </c>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -2944,9 +3812,13 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="4"/>
-      <c r="B89" s="9"/>
+    <row r="89" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>176</v>
+      </c>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -2972,9 +3844,13 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="4"/>
-      <c r="B90" s="9"/>
+    <row r="90" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>178</v>
+      </c>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -3000,9 +3876,13 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="4"/>
-      <c r="B91" s="9"/>
+    <row r="91" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>180</v>
+      </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -3028,9 +3908,13 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="4"/>
-      <c r="B92" s="9"/>
+    <row r="92" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -3056,9 +3940,13 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="4"/>
-      <c r="B93" s="9"/>
+    <row r="93" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>184</v>
+      </c>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -3084,9 +3972,13 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="4"/>
-      <c r="B94" s="9"/>
+    <row r="94" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>186</v>
+      </c>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -3112,9 +4004,13 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="4"/>
-      <c r="B95" s="9"/>
+    <row r="95" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>188</v>
+      </c>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -3140,9 +4036,13 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="4"/>
-      <c r="B96" s="9"/>
+    <row r="96" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>190</v>
+      </c>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -3168,9 +4068,13 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="4"/>
-      <c r="B97" s="9"/>
+    <row r="97" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>192</v>
+      </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -3196,9 +4100,13 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="4"/>
-      <c r="B98" s="9"/>
+    <row r="98" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>194</v>
+      </c>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -3224,9 +4132,13 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="4"/>
-      <c r="B99" s="9"/>
+    <row r="99" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>196</v>
+      </c>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -3252,9 +4164,13 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="4"/>
-      <c r="B100" s="9"/>
+    <row r="100" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -3280,7 +4196,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
       <c r="B101" s="9"/>
       <c r="C101" s="3"/>
@@ -3308,7 +4224,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="3"/>
@@ -3336,7 +4252,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="3"/>
@@ -3364,7 +4280,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="3"/>
@@ -3392,7 +4308,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
       <c r="B105" s="5"/>
       <c r="C105" s="3"/>
@@ -3420,7 +4336,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="4"/>
       <c r="B106" s="5"/>
       <c r="C106" s="3"/>
@@ -3448,7 +4364,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="4"/>
       <c r="B107" s="5"/>
       <c r="C107" s="3"/>
@@ -3476,7 +4392,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="4"/>
       <c r="B108" s="5"/>
       <c r="C108" s="3"/>
@@ -3504,7 +4420,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="3"/>
@@ -3532,7 +4448,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
       <c r="C110" s="3"/>
@@ -3560,7 +4476,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="4"/>
       <c r="B111" s="5"/>
       <c r="C111" s="3"/>
@@ -3588,7 +4504,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="4"/>
       <c r="B112" s="5"/>
       <c r="C112" s="3"/>
@@ -3616,7 +4532,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="3"/>
@@ -3644,7 +4560,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="3"/>
@@ -3672,7 +4588,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="3"/>
@@ -3700,7 +4616,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="3"/>
@@ -3728,7 +4644,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="3"/>
@@ -3756,7 +4672,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="3"/>
@@ -3784,7 +4700,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="3"/>
@@ -3812,7 +4728,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="3"/>
@@ -3840,7 +4756,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="3"/>
@@ -3868,7 +4784,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="3"/>
@@ -3896,7 +4812,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="3"/>
@@ -3924,7 +4840,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="3"/>
@@ -3952,7 +4868,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="3"/>
@@ -3980,7 +4896,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="3"/>
@@ -4008,7 +4924,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="3"/>
@@ -4036,7 +4952,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="3"/>
@@ -4064,7 +4980,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="3"/>
@@ -4092,7 +5008,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="3"/>
@@ -4120,7 +5036,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="3"/>
@@ -4148,7 +5064,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="3"/>
@@ -4176,7 +5092,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="3"/>
@@ -4204,7 +5120,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="3"/>
@@ -4232,7 +5148,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="3"/>
@@ -4260,7 +5176,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="3"/>
@@ -4288,7 +5204,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="3"/>
@@ -4316,7 +5232,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="3"/>
@@ -4344,7 +5260,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="3"/>
@@ -4372,7 +5288,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="3"/>
@@ -4400,7 +5316,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="3"/>
@@ -4428,7 +5344,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="3"/>
@@ -4456,7 +5372,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="3"/>
@@ -4484,7 +5400,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="3"/>
@@ -4512,7 +5428,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="3"/>
@@ -4540,7 +5456,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="3"/>
@@ -4568,7 +5484,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="3"/>
@@ -4596,7 +5512,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="3"/>
@@ -4624,7 +5540,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -4652,7 +5568,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -4680,7 +5596,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -4708,7 +5624,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -4736,7 +5652,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -4764,7 +5680,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -4792,7 +5708,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -4820,7 +5736,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -4848,7 +5764,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -4876,7 +5792,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -4904,7 +5820,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -4932,7 +5848,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -4960,7 +5876,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -4988,7 +5904,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5016,7 +5932,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -5044,7 +5960,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -5072,7 +5988,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -5100,7 +6016,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -5128,7 +6044,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -5156,7 +6072,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -5184,7 +6100,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -5212,7 +6128,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -5240,7 +6156,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -5268,7 +6184,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -5296,7 +6212,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -5324,7 +6240,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -5352,7 +6268,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -5380,7 +6296,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -5408,7 +6324,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -5436,7 +6352,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -5464,7 +6380,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -5492,7 +6408,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -5520,7 +6436,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -5548,7 +6464,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -5576,7 +6492,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -5604,7 +6520,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -5632,7 +6548,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -5660,7 +6576,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -5688,7 +6604,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -5716,7 +6632,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -5744,7 +6660,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -5772,7 +6688,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -5800,7 +6716,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -5828,7 +6744,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -5856,7 +6772,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -5884,7 +6800,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -5912,7 +6828,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -5940,7 +6856,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -5968,7 +6884,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -5996,7 +6912,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -6024,7 +6940,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -6052,7 +6968,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -6080,7 +6996,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -6108,7 +7024,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -6136,7 +7052,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -6164,7 +7080,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -6192,7 +7108,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -6220,7 +7136,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -6248,7 +7164,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -6276,7 +7192,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -6304,7 +7220,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -6332,7 +7248,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -6360,7 +7276,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -6388,7 +7304,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -6416,7 +7332,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -6444,7 +7360,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
     </row>
-    <row r="214" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -6472,7 +7388,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
     </row>
-    <row r="215" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -6500,7 +7416,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
     </row>
-    <row r="216" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -6528,7 +7444,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
     </row>
-    <row r="217" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -6556,7 +7472,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
     </row>
-    <row r="218" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -6584,7 +7500,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
     </row>
-    <row r="219" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -6612,7 +7528,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
     </row>
-    <row r="220" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -6640,7 +7556,7 @@
       <c r="Y220" s="3"/>
       <c r="Z220" s="3"/>
     </row>
-    <row r="221" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -6668,7 +7584,7 @@
       <c r="Y221" s="3"/>
       <c r="Z221" s="3"/>
     </row>
-    <row r="222" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -6696,7 +7612,7 @@
       <c r="Y222" s="3"/>
       <c r="Z222" s="3"/>
     </row>
-    <row r="223" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -6724,7 +7640,7 @@
       <c r="Y223" s="3"/>
       <c r="Z223" s="3"/>
     </row>
-    <row r="224" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -6752,7 +7668,7 @@
       <c r="Y224" s="3"/>
       <c r="Z224" s="3"/>
     </row>
-    <row r="225" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -6780,7 +7696,7 @@
       <c r="Y225" s="3"/>
       <c r="Z225" s="3"/>
     </row>
-    <row r="226" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -6808,7 +7724,7 @@
       <c r="Y226" s="3"/>
       <c r="Z226" s="3"/>
     </row>
-    <row r="227" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -6836,7 +7752,7 @@
       <c r="Y227" s="3"/>
       <c r="Z227" s="3"/>
     </row>
-    <row r="228" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -6864,7 +7780,7 @@
       <c r="Y228" s="3"/>
       <c r="Z228" s="3"/>
     </row>
-    <row r="229" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -6892,7 +7808,7 @@
       <c r="Y229" s="3"/>
       <c r="Z229" s="3"/>
     </row>
-    <row r="230" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -6920,7 +7836,7 @@
       <c r="Y230" s="3"/>
       <c r="Z230" s="3"/>
     </row>
-    <row r="231" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -6948,7 +7864,7 @@
       <c r="Y231" s="3"/>
       <c r="Z231" s="3"/>
     </row>
-    <row r="232" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -6976,7 +7892,7 @@
       <c r="Y232" s="3"/>
       <c r="Z232" s="3"/>
     </row>
-    <row r="233" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -7004,7 +7920,7 @@
       <c r="Y233" s="3"/>
       <c r="Z233" s="3"/>
     </row>
-    <row r="234" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -7032,7 +7948,7 @@
       <c r="Y234" s="3"/>
       <c r="Z234" s="3"/>
     </row>
-    <row r="235" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -7060,7 +7976,7 @@
       <c r="Y235" s="3"/>
       <c r="Z235" s="3"/>
     </row>
-    <row r="236" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -7088,7 +8004,7 @@
       <c r="Y236" s="3"/>
       <c r="Z236" s="3"/>
     </row>
-    <row r="237" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -7116,7 +8032,7 @@
       <c r="Y237" s="3"/>
       <c r="Z237" s="3"/>
     </row>
-    <row r="238" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -7144,7 +8060,7 @@
       <c r="Y238" s="3"/>
       <c r="Z238" s="3"/>
     </row>
-    <row r="239" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -7172,7 +8088,7 @@
       <c r="Y239" s="3"/>
       <c r="Z239" s="3"/>
     </row>
-    <row r="240" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -7200,7 +8116,7 @@
       <c r="Y240" s="3"/>
       <c r="Z240" s="3"/>
     </row>
-    <row r="241" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -7228,7 +8144,7 @@
       <c r="Y241" s="3"/>
       <c r="Z241" s="3"/>
     </row>
-    <row r="242" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -7256,7 +8172,7 @@
       <c r="Y242" s="3"/>
       <c r="Z242" s="3"/>
     </row>
-    <row r="243" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -7284,7 +8200,7 @@
       <c r="Y243" s="3"/>
       <c r="Z243" s="3"/>
     </row>
-    <row r="244" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -7312,7 +8228,7 @@
       <c r="Y244" s="3"/>
       <c r="Z244" s="3"/>
     </row>
-    <row r="245" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -7340,7 +8256,7 @@
       <c r="Y245" s="3"/>
       <c r="Z245" s="3"/>
     </row>
-    <row r="246" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -7368,7 +8284,7 @@
       <c r="Y246" s="3"/>
       <c r="Z246" s="3"/>
     </row>
-    <row r="247" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -7396,7 +8312,7 @@
       <c r="Y247" s="3"/>
       <c r="Z247" s="3"/>
     </row>
-    <row r="248" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -7424,7 +8340,7 @@
       <c r="Y248" s="3"/>
       <c r="Z248" s="3"/>
     </row>
-    <row r="249" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -7452,7 +8368,7 @@
       <c r="Y249" s="3"/>
       <c r="Z249" s="3"/>
     </row>
-    <row r="250" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -7480,7 +8396,7 @@
       <c r="Y250" s="3"/>
       <c r="Z250" s="3"/>
     </row>
-    <row r="251" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -7508,7 +8424,7 @@
       <c r="Y251" s="3"/>
       <c r="Z251" s="3"/>
     </row>
-    <row r="252" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -7536,7 +8452,7 @@
       <c r="Y252" s="3"/>
       <c r="Z252" s="3"/>
     </row>
-    <row r="253" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -7564,7 +8480,7 @@
       <c r="Y253" s="3"/>
       <c r="Z253" s="3"/>
     </row>
-    <row r="254" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -7592,7 +8508,7 @@
       <c r="Y254" s="3"/>
       <c r="Z254" s="3"/>
     </row>
-    <row r="255" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -7620,7 +8536,7 @@
       <c r="Y255" s="3"/>
       <c r="Z255" s="3"/>
     </row>
-    <row r="256" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -7648,7 +8564,7 @@
       <c r="Y256" s="3"/>
       <c r="Z256" s="3"/>
     </row>
-    <row r="257" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -7676,7 +8592,7 @@
       <c r="Y257" s="3"/>
       <c r="Z257" s="3"/>
     </row>
-    <row r="258" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -7704,7 +8620,7 @@
       <c r="Y258" s="3"/>
       <c r="Z258" s="3"/>
     </row>
-    <row r="259" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -7732,7 +8648,7 @@
       <c r="Y259" s="3"/>
       <c r="Z259" s="3"/>
     </row>
-    <row r="260" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -7760,7 +8676,7 @@
       <c r="Y260" s="3"/>
       <c r="Z260" s="3"/>
     </row>
-    <row r="261" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -7788,7 +8704,7 @@
       <c r="Y261" s="3"/>
       <c r="Z261" s="3"/>
     </row>
-    <row r="262" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -7816,7 +8732,7 @@
       <c r="Y262" s="3"/>
       <c r="Z262" s="3"/>
     </row>
-    <row r="263" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -7844,7 +8760,7 @@
       <c r="Y263" s="3"/>
       <c r="Z263" s="3"/>
     </row>
-    <row r="264" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -7872,7 +8788,7 @@
       <c r="Y264" s="3"/>
       <c r="Z264" s="3"/>
     </row>
-    <row r="265" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -7900,7 +8816,7 @@
       <c r="Y265" s="3"/>
       <c r="Z265" s="3"/>
     </row>
-    <row r="266" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -7928,7 +8844,7 @@
       <c r="Y266" s="3"/>
       <c r="Z266" s="3"/>
     </row>
-    <row r="267" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -7956,7 +8872,7 @@
       <c r="Y267" s="3"/>
       <c r="Z267" s="3"/>
     </row>
-    <row r="268" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -7984,7 +8900,7 @@
       <c r="Y268" s="3"/>
       <c r="Z268" s="3"/>
     </row>
-    <row r="269" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -8012,7 +8928,7 @@
       <c r="Y269" s="3"/>
       <c r="Z269" s="3"/>
     </row>
-    <row r="270" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -8040,7 +8956,7 @@
       <c r="Y270" s="3"/>
       <c r="Z270" s="3"/>
     </row>
-    <row r="271" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -8068,7 +8984,7 @@
       <c r="Y271" s="3"/>
       <c r="Z271" s="3"/>
     </row>
-    <row r="272" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -8096,7 +9012,7 @@
       <c r="Y272" s="3"/>
       <c r="Z272" s="3"/>
     </row>
-    <row r="273" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -8124,7 +9040,7 @@
       <c r="Y273" s="3"/>
       <c r="Z273" s="3"/>
     </row>
-    <row r="274" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -8152,7 +9068,7 @@
       <c r="Y274" s="3"/>
       <c r="Z274" s="3"/>
     </row>
-    <row r="275" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -8180,7 +9096,7 @@
       <c r="Y275" s="3"/>
       <c r="Z275" s="3"/>
     </row>
-    <row r="276" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -8208,7 +9124,7 @@
       <c r="Y276" s="3"/>
       <c r="Z276" s="3"/>
     </row>
-    <row r="277" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -8236,7 +9152,7 @@
       <c r="Y277" s="3"/>
       <c r="Z277" s="3"/>
     </row>
-    <row r="278" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -8264,7 +9180,7 @@
       <c r="Y278" s="3"/>
       <c r="Z278" s="3"/>
     </row>
-    <row r="279" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -8292,7 +9208,7 @@
       <c r="Y279" s="3"/>
       <c r="Z279" s="3"/>
     </row>
-    <row r="280" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -8320,7 +9236,7 @@
       <c r="Y280" s="3"/>
       <c r="Z280" s="3"/>
     </row>
-    <row r="281" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -8348,7 +9264,7 @@
       <c r="Y281" s="3"/>
       <c r="Z281" s="3"/>
     </row>
-    <row r="282" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -8376,7 +9292,7 @@
       <c r="Y282" s="3"/>
       <c r="Z282" s="3"/>
     </row>
-    <row r="283" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -8404,7 +9320,7 @@
       <c r="Y283" s="3"/>
       <c r="Z283" s="3"/>
     </row>
-    <row r="284" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -8432,7 +9348,7 @@
       <c r="Y284" s="3"/>
       <c r="Z284" s="3"/>
     </row>
-    <row r="285" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -8460,7 +9376,7 @@
       <c r="Y285" s="3"/>
       <c r="Z285" s="3"/>
     </row>
-    <row r="286" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -8488,7 +9404,7 @@
       <c r="Y286" s="3"/>
       <c r="Z286" s="3"/>
     </row>
-    <row r="287" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -8516,7 +9432,7 @@
       <c r="Y287" s="3"/>
       <c r="Z287" s="3"/>
     </row>
-    <row r="288" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -8544,7 +9460,7 @@
       <c r="Y288" s="3"/>
       <c r="Z288" s="3"/>
     </row>
-    <row r="289" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -8572,7 +9488,7 @@
       <c r="Y289" s="3"/>
       <c r="Z289" s="3"/>
     </row>
-    <row r="290" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -8600,7 +9516,7 @@
       <c r="Y290" s="3"/>
       <c r="Z290" s="3"/>
     </row>
-    <row r="291" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -8628,7 +9544,7 @@
       <c r="Y291" s="3"/>
       <c r="Z291" s="3"/>
     </row>
-    <row r="292" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -8656,7 +9572,7 @@
       <c r="Y292" s="3"/>
       <c r="Z292" s="3"/>
     </row>
-    <row r="293" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -8684,7 +9600,7 @@
       <c r="Y293" s="3"/>
       <c r="Z293" s="3"/>
     </row>
-    <row r="294" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -8712,7 +9628,7 @@
       <c r="Y294" s="3"/>
       <c r="Z294" s="3"/>
     </row>
-    <row r="295" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -8740,7 +9656,7 @@
       <c r="Y295" s="3"/>
       <c r="Z295" s="3"/>
     </row>
-    <row r="296" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -8768,7 +9684,7 @@
       <c r="Y296" s="3"/>
       <c r="Z296" s="3"/>
     </row>
-    <row r="297" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -8796,7 +9712,7 @@
       <c r="Y297" s="3"/>
       <c r="Z297" s="3"/>
     </row>
-    <row r="298" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -8824,7 +9740,7 @@
       <c r="Y298" s="3"/>
       <c r="Z298" s="3"/>
     </row>
-    <row r="299" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -8852,7 +9768,7 @@
       <c r="Y299" s="3"/>
       <c r="Z299" s="3"/>
     </row>
-    <row r="300" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -8880,7 +9796,7 @@
       <c r="Y300" s="3"/>
       <c r="Z300" s="3"/>
     </row>
-    <row r="301" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -8908,7 +9824,7 @@
       <c r="Y301" s="3"/>
       <c r="Z301" s="3"/>
     </row>
-    <row r="302" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -8936,7 +9852,7 @@
       <c r="Y302" s="3"/>
       <c r="Z302" s="3"/>
     </row>
-    <row r="303" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -8964,7 +9880,7 @@
       <c r="Y303" s="3"/>
       <c r="Z303" s="3"/>
     </row>
-    <row r="304" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -8992,7 +9908,7 @@
       <c r="Y304" s="3"/>
       <c r="Z304" s="3"/>
     </row>
-    <row r="305" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -9020,7 +9936,7 @@
       <c r="Y305" s="3"/>
       <c r="Z305" s="3"/>
     </row>
-    <row r="306" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -9048,7 +9964,7 @@
       <c r="Y306" s="3"/>
       <c r="Z306" s="3"/>
     </row>
-    <row r="307" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -9076,7 +9992,7 @@
       <c r="Y307" s="3"/>
       <c r="Z307" s="3"/>
     </row>
-    <row r="308" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -9104,7 +10020,7 @@
       <c r="Y308" s="3"/>
       <c r="Z308" s="3"/>
     </row>
-    <row r="309" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -9132,7 +10048,7 @@
       <c r="Y309" s="3"/>
       <c r="Z309" s="3"/>
     </row>
-    <row r="310" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -9160,7 +10076,7 @@
       <c r="Y310" s="3"/>
       <c r="Z310" s="3"/>
     </row>
-    <row r="311" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -9188,7 +10104,7 @@
       <c r="Y311" s="3"/>
       <c r="Z311" s="3"/>
     </row>
-    <row r="312" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -9216,7 +10132,7 @@
       <c r="Y312" s="3"/>
       <c r="Z312" s="3"/>
     </row>
-    <row r="313" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -9244,7 +10160,7 @@
       <c r="Y313" s="3"/>
       <c r="Z313" s="3"/>
     </row>
-    <row r="314" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -9272,7 +10188,7 @@
       <c r="Y314" s="3"/>
       <c r="Z314" s="3"/>
     </row>
-    <row r="315" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -9300,7 +10216,7 @@
       <c r="Y315" s="3"/>
       <c r="Z315" s="3"/>
     </row>
-    <row r="316" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -9328,7 +10244,7 @@
       <c r="Y316" s="3"/>
       <c r="Z316" s="3"/>
     </row>
-    <row r="317" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -9356,7 +10272,7 @@
       <c r="Y317" s="3"/>
       <c r="Z317" s="3"/>
     </row>
-    <row r="318" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -9384,7 +10300,7 @@
       <c r="Y318" s="3"/>
       <c r="Z318" s="3"/>
     </row>
-    <row r="319" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -9412,7 +10328,7 @@
       <c r="Y319" s="3"/>
       <c r="Z319" s="3"/>
     </row>
-    <row r="320" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -9440,7 +10356,7 @@
       <c r="Y320" s="3"/>
       <c r="Z320" s="3"/>
     </row>
-    <row r="321" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -9468,7 +10384,7 @@
       <c r="Y321" s="3"/>
       <c r="Z321" s="3"/>
     </row>
-    <row r="322" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -9496,7 +10412,7 @@
       <c r="Y322" s="3"/>
       <c r="Z322" s="3"/>
     </row>
-    <row r="323" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -9524,7 +10440,7 @@
       <c r="Y323" s="3"/>
       <c r="Z323" s="3"/>
     </row>
-    <row r="324" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -9552,7 +10468,7 @@
       <c r="Y324" s="3"/>
       <c r="Z324" s="3"/>
     </row>
-    <row r="325" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -9580,7 +10496,7 @@
       <c r="Y325" s="3"/>
       <c r="Z325" s="3"/>
     </row>
-    <row r="326" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -9608,7 +10524,7 @@
       <c r="Y326" s="3"/>
       <c r="Z326" s="3"/>
     </row>
-    <row r="327" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -9636,7 +10552,7 @@
       <c r="Y327" s="3"/>
       <c r="Z327" s="3"/>
     </row>
-    <row r="328" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -9664,7 +10580,7 @@
       <c r="Y328" s="3"/>
       <c r="Z328" s="3"/>
     </row>
-    <row r="329" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -9692,7 +10608,7 @@
       <c r="Y329" s="3"/>
       <c r="Z329" s="3"/>
     </row>
-    <row r="330" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -9720,7 +10636,7 @@
       <c r="Y330" s="3"/>
       <c r="Z330" s="3"/>
     </row>
-    <row r="331" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -9748,7 +10664,7 @@
       <c r="Y331" s="3"/>
       <c r="Z331" s="3"/>
     </row>
-    <row r="332" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -9776,7 +10692,7 @@
       <c r="Y332" s="3"/>
       <c r="Z332" s="3"/>
     </row>
-    <row r="333" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -9804,7 +10720,7 @@
       <c r="Y333" s="3"/>
       <c r="Z333" s="3"/>
     </row>
-    <row r="334" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -9832,7 +10748,7 @@
       <c r="Y334" s="3"/>
       <c r="Z334" s="3"/>
     </row>
-    <row r="335" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -9860,7 +10776,7 @@
       <c r="Y335" s="3"/>
       <c r="Z335" s="3"/>
     </row>
-    <row r="336" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -9888,7 +10804,7 @@
       <c r="Y336" s="3"/>
       <c r="Z336" s="3"/>
     </row>
-    <row r="337" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -9916,7 +10832,7 @@
       <c r="Y337" s="3"/>
       <c r="Z337" s="3"/>
     </row>
-    <row r="338" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -9944,7 +10860,7 @@
       <c r="Y338" s="3"/>
       <c r="Z338" s="3"/>
     </row>
-    <row r="339" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -9972,7 +10888,7 @@
       <c r="Y339" s="3"/>
       <c r="Z339" s="3"/>
     </row>
-    <row r="340" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -10000,7 +10916,7 @@
       <c r="Y340" s="3"/>
       <c r="Z340" s="3"/>
     </row>
-    <row r="341" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -10028,7 +10944,7 @@
       <c r="Y341" s="3"/>
       <c r="Z341" s="3"/>
     </row>
-    <row r="342" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -10056,7 +10972,7 @@
       <c r="Y342" s="3"/>
       <c r="Z342" s="3"/>
     </row>
-    <row r="343" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -10084,7 +11000,7 @@
       <c r="Y343" s="3"/>
       <c r="Z343" s="3"/>
     </row>
-    <row r="344" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -10112,7 +11028,7 @@
       <c r="Y344" s="3"/>
       <c r="Z344" s="3"/>
     </row>
-    <row r="345" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -10140,7 +11056,7 @@
       <c r="Y345" s="3"/>
       <c r="Z345" s="3"/>
     </row>
-    <row r="346" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -10168,7 +11084,7 @@
       <c r="Y346" s="3"/>
       <c r="Z346" s="3"/>
     </row>
-    <row r="347" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -10196,7 +11112,7 @@
       <c r="Y347" s="3"/>
       <c r="Z347" s="3"/>
     </row>
-    <row r="348" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -10224,7 +11140,7 @@
       <c r="Y348" s="3"/>
       <c r="Z348" s="3"/>
     </row>
-    <row r="349" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -10252,7 +11168,7 @@
       <c r="Y349" s="3"/>
       <c r="Z349" s="3"/>
     </row>
-    <row r="350" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -10280,7 +11196,7 @@
       <c r="Y350" s="3"/>
       <c r="Z350" s="3"/>
     </row>
-    <row r="351" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -10308,7 +11224,7 @@
       <c r="Y351" s="3"/>
       <c r="Z351" s="3"/>
     </row>
-    <row r="352" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -10336,7 +11252,7 @@
       <c r="Y352" s="3"/>
       <c r="Z352" s="3"/>
     </row>
-    <row r="353" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -10364,7 +11280,7 @@
       <c r="Y353" s="3"/>
       <c r="Z353" s="3"/>
     </row>
-    <row r="354" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -10392,7 +11308,7 @@
       <c r="Y354" s="3"/>
       <c r="Z354" s="3"/>
     </row>
-    <row r="355" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -10420,7 +11336,7 @@
       <c r="Y355" s="3"/>
       <c r="Z355" s="3"/>
     </row>
-    <row r="356" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -10448,7 +11364,7 @@
       <c r="Y356" s="3"/>
       <c r="Z356" s="3"/>
     </row>
-    <row r="357" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -10476,7 +11392,7 @@
       <c r="Y357" s="3"/>
       <c r="Z357" s="3"/>
     </row>
-    <row r="358" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -10504,7 +11420,7 @@
       <c r="Y358" s="3"/>
       <c r="Z358" s="3"/>
     </row>
-    <row r="359" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -10532,7 +11448,7 @@
       <c r="Y359" s="3"/>
       <c r="Z359" s="3"/>
     </row>
-    <row r="360" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -10560,7 +11476,7 @@
       <c r="Y360" s="3"/>
       <c r="Z360" s="3"/>
     </row>
-    <row r="361" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -10588,7 +11504,7 @@
       <c r="Y361" s="3"/>
       <c r="Z361" s="3"/>
     </row>
-    <row r="362" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -10616,7 +11532,7 @@
       <c r="Y362" s="3"/>
       <c r="Z362" s="3"/>
     </row>
-    <row r="363" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -10644,7 +11560,7 @@
       <c r="Y363" s="3"/>
       <c r="Z363" s="3"/>
     </row>
-    <row r="364" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -10672,7 +11588,7 @@
       <c r="Y364" s="3"/>
       <c r="Z364" s="3"/>
     </row>
-    <row r="365" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -10700,7 +11616,7 @@
       <c r="Y365" s="3"/>
       <c r="Z365" s="3"/>
     </row>
-    <row r="366" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -10728,7 +11644,7 @@
       <c r="Y366" s="3"/>
       <c r="Z366" s="3"/>
     </row>
-    <row r="367" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -10756,7 +11672,7 @@
       <c r="Y367" s="3"/>
       <c r="Z367" s="3"/>
     </row>
-    <row r="368" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -10784,7 +11700,7 @@
       <c r="Y368" s="3"/>
       <c r="Z368" s="3"/>
     </row>
-    <row r="369" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -10812,7 +11728,7 @@
       <c r="Y369" s="3"/>
       <c r="Z369" s="3"/>
     </row>
-    <row r="370" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -10840,7 +11756,7 @@
       <c r="Y370" s="3"/>
       <c r="Z370" s="3"/>
     </row>
-    <row r="371" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -10868,7 +11784,7 @@
       <c r="Y371" s="3"/>
       <c r="Z371" s="3"/>
     </row>
-    <row r="372" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -10896,7 +11812,7 @@
       <c r="Y372" s="3"/>
       <c r="Z372" s="3"/>
     </row>
-    <row r="373" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -10924,7 +11840,7 @@
       <c r="Y373" s="3"/>
       <c r="Z373" s="3"/>
     </row>
-    <row r="374" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -10952,7 +11868,7 @@
       <c r="Y374" s="3"/>
       <c r="Z374" s="3"/>
     </row>
-    <row r="375" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -10980,7 +11896,7 @@
       <c r="Y375" s="3"/>
       <c r="Z375" s="3"/>
     </row>
-    <row r="376" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -11008,7 +11924,7 @@
       <c r="Y376" s="3"/>
       <c r="Z376" s="3"/>
     </row>
-    <row r="377" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -11036,7 +11952,7 @@
       <c r="Y377" s="3"/>
       <c r="Z377" s="3"/>
     </row>
-    <row r="378" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -11064,7 +11980,7 @@
       <c r="Y378" s="3"/>
       <c r="Z378" s="3"/>
     </row>
-    <row r="379" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -11092,7 +12008,7 @@
       <c r="Y379" s="3"/>
       <c r="Z379" s="3"/>
     </row>
-    <row r="380" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -11120,7 +12036,7 @@
       <c r="Y380" s="3"/>
       <c r="Z380" s="3"/>
     </row>
-    <row r="381" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -11148,7 +12064,7 @@
       <c r="Y381" s="3"/>
       <c r="Z381" s="3"/>
     </row>
-    <row r="382" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -11176,7 +12092,7 @@
       <c r="Y382" s="3"/>
       <c r="Z382" s="3"/>
     </row>
-    <row r="383" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -11204,7 +12120,7 @@
       <c r="Y383" s="3"/>
       <c r="Z383" s="3"/>
     </row>
-    <row r="384" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -11232,7 +12148,7 @@
       <c r="Y384" s="3"/>
       <c r="Z384" s="3"/>
     </row>
-    <row r="385" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -11260,7 +12176,7 @@
       <c r="Y385" s="3"/>
       <c r="Z385" s="3"/>
     </row>
-    <row r="386" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -11288,7 +12204,7 @@
       <c r="Y386" s="3"/>
       <c r="Z386" s="3"/>
     </row>
-    <row r="387" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -11316,7 +12232,7 @@
       <c r="Y387" s="3"/>
       <c r="Z387" s="3"/>
     </row>
-    <row r="388" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -11344,7 +12260,7 @@
       <c r="Y388" s="3"/>
       <c r="Z388" s="3"/>
     </row>
-    <row r="389" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -11372,7 +12288,7 @@
       <c r="Y389" s="3"/>
       <c r="Z389" s="3"/>
     </row>
-    <row r="390" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -11400,7 +12316,7 @@
       <c r="Y390" s="3"/>
       <c r="Z390" s="3"/>
     </row>
-    <row r="391" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -11428,7 +12344,7 @@
       <c r="Y391" s="3"/>
       <c r="Z391" s="3"/>
     </row>
-    <row r="392" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -11456,7 +12372,7 @@
       <c r="Y392" s="3"/>
       <c r="Z392" s="3"/>
     </row>
-    <row r="393" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -11484,7 +12400,7 @@
       <c r="Y393" s="3"/>
       <c r="Z393" s="3"/>
     </row>
-    <row r="394" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -11512,7 +12428,7 @@
       <c r="Y394" s="3"/>
       <c r="Z394" s="3"/>
     </row>
-    <row r="395" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -11540,7 +12456,7 @@
       <c r="Y395" s="3"/>
       <c r="Z395" s="3"/>
     </row>
-    <row r="396" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -11568,7 +12484,7 @@
       <c r="Y396" s="3"/>
       <c r="Z396" s="3"/>
     </row>
-    <row r="397" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -11596,7 +12512,7 @@
       <c r="Y397" s="3"/>
       <c r="Z397" s="3"/>
     </row>
-    <row r="398" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -11624,7 +12540,7 @@
       <c r="Y398" s="3"/>
       <c r="Z398" s="3"/>
     </row>
-    <row r="399" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -11652,7 +12568,7 @@
       <c r="Y399" s="3"/>
       <c r="Z399" s="3"/>
     </row>
-    <row r="400" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -11680,7 +12596,7 @@
       <c r="Y400" s="3"/>
       <c r="Z400" s="3"/>
     </row>
-    <row r="401" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -11708,7 +12624,7 @@
       <c r="Y401" s="3"/>
       <c r="Z401" s="3"/>
     </row>
-    <row r="402" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -11736,7 +12652,7 @@
       <c r="Y402" s="3"/>
       <c r="Z402" s="3"/>
     </row>
-    <row r="403" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -11764,7 +12680,7 @@
       <c r="Y403" s="3"/>
       <c r="Z403" s="3"/>
     </row>
-    <row r="404" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -11792,7 +12708,7 @@
       <c r="Y404" s="3"/>
       <c r="Z404" s="3"/>
     </row>
-    <row r="405" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -11820,7 +12736,7 @@
       <c r="Y405" s="3"/>
       <c r="Z405" s="3"/>
     </row>
-    <row r="406" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -11848,7 +12764,7 @@
       <c r="Y406" s="3"/>
       <c r="Z406" s="3"/>
     </row>
-    <row r="407" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -11876,7 +12792,7 @@
       <c r="Y407" s="3"/>
       <c r="Z407" s="3"/>
     </row>
-    <row r="408" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -11904,7 +12820,7 @@
       <c r="Y408" s="3"/>
       <c r="Z408" s="3"/>
     </row>
-    <row r="409" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -11932,7 +12848,7 @@
       <c r="Y409" s="3"/>
       <c r="Z409" s="3"/>
     </row>
-    <row r="410" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -11960,7 +12876,7 @@
       <c r="Y410" s="3"/>
       <c r="Z410" s="3"/>
     </row>
-    <row r="411" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -11988,7 +12904,7 @@
       <c r="Y411" s="3"/>
       <c r="Z411" s="3"/>
     </row>
-    <row r="412" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -12016,7 +12932,7 @@
       <c r="Y412" s="3"/>
       <c r="Z412" s="3"/>
     </row>
-    <row r="413" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -12044,7 +12960,7 @@
       <c r="Y413" s="3"/>
       <c r="Z413" s="3"/>
     </row>
-    <row r="414" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -12072,7 +12988,7 @@
       <c r="Y414" s="3"/>
       <c r="Z414" s="3"/>
     </row>
-    <row r="415" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -12100,7 +13016,7 @@
       <c r="Y415" s="3"/>
       <c r="Z415" s="3"/>
     </row>
-    <row r="416" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -12128,7 +13044,7 @@
       <c r="Y416" s="3"/>
       <c r="Z416" s="3"/>
     </row>
-    <row r="417" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -12156,7 +13072,7 @@
       <c r="Y417" s="3"/>
       <c r="Z417" s="3"/>
     </row>
-    <row r="418" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -12184,7 +13100,7 @@
       <c r="Y418" s="3"/>
       <c r="Z418" s="3"/>
     </row>
-    <row r="419" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -12212,7 +13128,7 @@
       <c r="Y419" s="3"/>
       <c r="Z419" s="3"/>
     </row>
-    <row r="420" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -12240,7 +13156,7 @@
       <c r="Y420" s="3"/>
       <c r="Z420" s="3"/>
     </row>
-    <row r="421" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -12268,7 +13184,7 @@
       <c r="Y421" s="3"/>
       <c r="Z421" s="3"/>
     </row>
-    <row r="422" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -12296,7 +13212,7 @@
       <c r="Y422" s="3"/>
       <c r="Z422" s="3"/>
     </row>
-    <row r="423" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -12324,7 +13240,7 @@
       <c r="Y423" s="3"/>
       <c r="Z423" s="3"/>
     </row>
-    <row r="424" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -12352,7 +13268,7 @@
       <c r="Y424" s="3"/>
       <c r="Z424" s="3"/>
     </row>
-    <row r="425" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -12380,7 +13296,7 @@
       <c r="Y425" s="3"/>
       <c r="Z425" s="3"/>
     </row>
-    <row r="426" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -12408,7 +13324,7 @@
       <c r="Y426" s="3"/>
       <c r="Z426" s="3"/>
     </row>
-    <row r="427" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -12436,7 +13352,7 @@
       <c r="Y427" s="3"/>
       <c r="Z427" s="3"/>
     </row>
-    <row r="428" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -12464,7 +13380,7 @@
       <c r="Y428" s="3"/>
       <c r="Z428" s="3"/>
     </row>
-    <row r="429" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -12492,7 +13408,7 @@
       <c r="Y429" s="3"/>
       <c r="Z429" s="3"/>
     </row>
-    <row r="430" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -12520,7 +13436,7 @@
       <c r="Y430" s="3"/>
       <c r="Z430" s="3"/>
     </row>
-    <row r="431" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -12548,7 +13464,7 @@
       <c r="Y431" s="3"/>
       <c r="Z431" s="3"/>
     </row>
-    <row r="432" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -12576,7 +13492,7 @@
       <c r="Y432" s="3"/>
       <c r="Z432" s="3"/>
     </row>
-    <row r="433" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -12604,7 +13520,7 @@
       <c r="Y433" s="3"/>
       <c r="Z433" s="3"/>
     </row>
-    <row r="434" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -12632,7 +13548,7 @@
       <c r="Y434" s="3"/>
       <c r="Z434" s="3"/>
     </row>
-    <row r="435" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -12660,7 +13576,7 @@
       <c r="Y435" s="3"/>
       <c r="Z435" s="3"/>
     </row>
-    <row r="436" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -12688,7 +13604,7 @@
       <c r="Y436" s="3"/>
       <c r="Z436" s="3"/>
     </row>
-    <row r="437" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -12716,7 +13632,7 @@
       <c r="Y437" s="3"/>
       <c r="Z437" s="3"/>
     </row>
-    <row r="438" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -12744,7 +13660,7 @@
       <c r="Y438" s="3"/>
       <c r="Z438" s="3"/>
     </row>
-    <row r="439" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -12772,7 +13688,7 @@
       <c r="Y439" s="3"/>
       <c r="Z439" s="3"/>
     </row>
-    <row r="440" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -12800,7 +13716,7 @@
       <c r="Y440" s="3"/>
       <c r="Z440" s="3"/>
     </row>
-    <row r="441" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -12828,7 +13744,7 @@
       <c r="Y441" s="3"/>
       <c r="Z441" s="3"/>
     </row>
-    <row r="442" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -12856,7 +13772,7 @@
       <c r="Y442" s="3"/>
       <c r="Z442" s="3"/>
     </row>
-    <row r="443" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -12884,7 +13800,7 @@
       <c r="Y443" s="3"/>
       <c r="Z443" s="3"/>
     </row>
-    <row r="444" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -12912,7 +13828,7 @@
       <c r="Y444" s="3"/>
       <c r="Z444" s="3"/>
     </row>
-    <row r="445" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -12940,7 +13856,7 @@
       <c r="Y445" s="3"/>
       <c r="Z445" s="3"/>
     </row>
-    <row r="446" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -12968,7 +13884,7 @@
       <c r="Y446" s="3"/>
       <c r="Z446" s="3"/>
     </row>
-    <row r="447" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -12996,7 +13912,7 @@
       <c r="Y447" s="3"/>
       <c r="Z447" s="3"/>
     </row>
-    <row r="448" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -13024,7 +13940,7 @@
       <c r="Y448" s="3"/>
       <c r="Z448" s="3"/>
     </row>
-    <row r="449" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -13052,7 +13968,7 @@
       <c r="Y449" s="3"/>
       <c r="Z449" s="3"/>
     </row>
-    <row r="450" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -13080,7 +13996,7 @@
       <c r="Y450" s="3"/>
       <c r="Z450" s="3"/>
     </row>
-    <row r="451" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -13108,7 +14024,7 @@
       <c r="Y451" s="3"/>
       <c r="Z451" s="3"/>
     </row>
-    <row r="452" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -13136,7 +14052,7 @@
       <c r="Y452" s="3"/>
       <c r="Z452" s="3"/>
     </row>
-    <row r="453" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -13164,7 +14080,7 @@
       <c r="Y453" s="3"/>
       <c r="Z453" s="3"/>
     </row>
-    <row r="454" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -13192,7 +14108,7 @@
       <c r="Y454" s="3"/>
       <c r="Z454" s="3"/>
     </row>
-    <row r="455" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -13220,7 +14136,7 @@
       <c r="Y455" s="3"/>
       <c r="Z455" s="3"/>
     </row>
-    <row r="456" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -13248,7 +14164,7 @@
       <c r="Y456" s="3"/>
       <c r="Z456" s="3"/>
     </row>
-    <row r="457" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -13276,7 +14192,7 @@
       <c r="Y457" s="3"/>
       <c r="Z457" s="3"/>
     </row>
-    <row r="458" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -13304,7 +14220,7 @@
       <c r="Y458" s="3"/>
       <c r="Z458" s="3"/>
     </row>
-    <row r="459" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -13332,7 +14248,7 @@
       <c r="Y459" s="3"/>
       <c r="Z459" s="3"/>
     </row>
-    <row r="460" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -13360,7 +14276,7 @@
       <c r="Y460" s="3"/>
       <c r="Z460" s="3"/>
     </row>
-    <row r="461" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -13388,7 +14304,7 @@
       <c r="Y461" s="3"/>
       <c r="Z461" s="3"/>
     </row>
-    <row r="462" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -13416,7 +14332,7 @@
       <c r="Y462" s="3"/>
       <c r="Z462" s="3"/>
     </row>
-    <row r="463" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -13444,7 +14360,7 @@
       <c r="Y463" s="3"/>
       <c r="Z463" s="3"/>
     </row>
-    <row r="464" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -13472,7 +14388,7 @@
       <c r="Y464" s="3"/>
       <c r="Z464" s="3"/>
     </row>
-    <row r="465" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -13500,7 +14416,7 @@
       <c r="Y465" s="3"/>
       <c r="Z465" s="3"/>
     </row>
-    <row r="466" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -13528,7 +14444,7 @@
       <c r="Y466" s="3"/>
       <c r="Z466" s="3"/>
     </row>
-    <row r="467" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -13556,7 +14472,7 @@
       <c r="Y467" s="3"/>
       <c r="Z467" s="3"/>
     </row>
-    <row r="468" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -13584,7 +14500,7 @@
       <c r="Y468" s="3"/>
       <c r="Z468" s="3"/>
     </row>
-    <row r="469" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -13612,7 +14528,7 @@
       <c r="Y469" s="3"/>
       <c r="Z469" s="3"/>
     </row>
-    <row r="470" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -13640,7 +14556,7 @@
       <c r="Y470" s="3"/>
       <c r="Z470" s="3"/>
     </row>
-    <row r="471" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -13668,7 +14584,7 @@
       <c r="Y471" s="3"/>
       <c r="Z471" s="3"/>
     </row>
-    <row r="472" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -13696,7 +14612,7 @@
       <c r="Y472" s="3"/>
       <c r="Z472" s="3"/>
     </row>
-    <row r="473" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -13724,7 +14640,7 @@
       <c r="Y473" s="3"/>
       <c r="Z473" s="3"/>
     </row>
-    <row r="474" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -13752,7 +14668,7 @@
       <c r="Y474" s="3"/>
       <c r="Z474" s="3"/>
     </row>
-    <row r="475" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -13780,7 +14696,7 @@
       <c r="Y475" s="3"/>
       <c r="Z475" s="3"/>
     </row>
-    <row r="476" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -13808,7 +14724,7 @@
       <c r="Y476" s="3"/>
       <c r="Z476" s="3"/>
     </row>
-    <row r="477" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -13836,7 +14752,7 @@
       <c r="Y477" s="3"/>
       <c r="Z477" s="3"/>
     </row>
-    <row r="478" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -13864,7 +14780,7 @@
       <c r="Y478" s="3"/>
       <c r="Z478" s="3"/>
     </row>
-    <row r="479" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -13892,7 +14808,7 @@
       <c r="Y479" s="3"/>
       <c r="Z479" s="3"/>
     </row>
-    <row r="480" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -13920,7 +14836,7 @@
       <c r="Y480" s="3"/>
       <c r="Z480" s="3"/>
     </row>
-    <row r="481" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -13948,7 +14864,7 @@
       <c r="Y481" s="3"/>
       <c r="Z481" s="3"/>
     </row>
-    <row r="482" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -13976,7 +14892,7 @@
       <c r="Y482" s="3"/>
       <c r="Z482" s="3"/>
     </row>
-    <row r="483" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -14004,7 +14920,7 @@
       <c r="Y483" s="3"/>
       <c r="Z483" s="3"/>
     </row>
-    <row r="484" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -14032,7 +14948,7 @@
       <c r="Y484" s="3"/>
       <c r="Z484" s="3"/>
     </row>
-    <row r="485" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -14060,7 +14976,7 @@
       <c r="Y485" s="3"/>
       <c r="Z485" s="3"/>
     </row>
-    <row r="486" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -14088,7 +15004,7 @@
       <c r="Y486" s="3"/>
       <c r="Z486" s="3"/>
     </row>
-    <row r="487" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -14116,7 +15032,7 @@
       <c r="Y487" s="3"/>
       <c r="Z487" s="3"/>
     </row>
-    <row r="488" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -14144,7 +15060,7 @@
       <c r="Y488" s="3"/>
       <c r="Z488" s="3"/>
     </row>
-    <row r="489" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -14172,7 +15088,7 @@
       <c r="Y489" s="3"/>
       <c r="Z489" s="3"/>
     </row>
-    <row r="490" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -14200,7 +15116,7 @@
       <c r="Y490" s="3"/>
       <c r="Z490" s="3"/>
     </row>
-    <row r="491" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -14228,7 +15144,7 @@
       <c r="Y491" s="3"/>
       <c r="Z491" s="3"/>
     </row>
-    <row r="492" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -14256,7 +15172,7 @@
       <c r="Y492" s="3"/>
       <c r="Z492" s="3"/>
     </row>
-    <row r="493" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -14284,7 +15200,7 @@
       <c r="Y493" s="3"/>
       <c r="Z493" s="3"/>
     </row>
-    <row r="494" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -14312,7 +15228,7 @@
       <c r="Y494" s="3"/>
       <c r="Z494" s="3"/>
     </row>
-    <row r="495" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -14340,7 +15256,7 @@
       <c r="Y495" s="3"/>
       <c r="Z495" s="3"/>
     </row>
-    <row r="496" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -14368,7 +15284,7 @@
       <c r="Y496" s="3"/>
       <c r="Z496" s="3"/>
     </row>
-    <row r="497" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -14396,7 +15312,7 @@
       <c r="Y497" s="3"/>
       <c r="Z497" s="3"/>
     </row>
-    <row r="498" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -14424,7 +15340,7 @@
       <c r="Y498" s="3"/>
       <c r="Z498" s="3"/>
     </row>
-    <row r="499" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -14452,7 +15368,7 @@
       <c r="Y499" s="3"/>
       <c r="Z499" s="3"/>
     </row>
-    <row r="500" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -14480,7 +15396,7 @@
       <c r="Y500" s="3"/>
       <c r="Z500" s="3"/>
     </row>
-    <row r="501" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -14508,7 +15424,7 @@
       <c r="Y501" s="3"/>
       <c r="Z501" s="3"/>
     </row>
-    <row r="502" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -14536,7 +15452,7 @@
       <c r="Y502" s="3"/>
       <c r="Z502" s="3"/>
     </row>
-    <row r="503" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -14564,7 +15480,7 @@
       <c r="Y503" s="3"/>
       <c r="Z503" s="3"/>
     </row>
-    <row r="504" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -14592,7 +15508,7 @@
       <c r="Y504" s="3"/>
       <c r="Z504" s="3"/>
     </row>
-    <row r="505" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -14620,7 +15536,7 @@
       <c r="Y505" s="3"/>
       <c r="Z505" s="3"/>
     </row>
-    <row r="506" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -14648,7 +15564,7 @@
       <c r="Y506" s="3"/>
       <c r="Z506" s="3"/>
     </row>
-    <row r="507" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -14676,7 +15592,7 @@
       <c r="Y507" s="3"/>
       <c r="Z507" s="3"/>
     </row>
-    <row r="508" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -14704,7 +15620,7 @@
       <c r="Y508" s="3"/>
       <c r="Z508" s="3"/>
     </row>
-    <row r="509" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -14732,7 +15648,7 @@
       <c r="Y509" s="3"/>
       <c r="Z509" s="3"/>
     </row>
-    <row r="510" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -14760,7 +15676,7 @@
       <c r="Y510" s="3"/>
       <c r="Z510" s="3"/>
     </row>
-    <row r="511" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -14788,7 +15704,7 @@
       <c r="Y511" s="3"/>
       <c r="Z511" s="3"/>
     </row>
-    <row r="512" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -14816,7 +15732,7 @@
       <c r="Y512" s="3"/>
       <c r="Z512" s="3"/>
     </row>
-    <row r="513" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -14844,7 +15760,7 @@
       <c r="Y513" s="3"/>
       <c r="Z513" s="3"/>
     </row>
-    <row r="514" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -14872,7 +15788,7 @@
       <c r="Y514" s="3"/>
       <c r="Z514" s="3"/>
     </row>
-    <row r="515" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -14900,7 +15816,7 @@
       <c r="Y515" s="3"/>
       <c r="Z515" s="3"/>
     </row>
-    <row r="516" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -14928,7 +15844,7 @@
       <c r="Y516" s="3"/>
       <c r="Z516" s="3"/>
     </row>
-    <row r="517" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -14956,7 +15872,7 @@
       <c r="Y517" s="3"/>
       <c r="Z517" s="3"/>
     </row>
-    <row r="518" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -14984,7 +15900,7 @@
       <c r="Y518" s="3"/>
       <c r="Z518" s="3"/>
     </row>
-    <row r="519" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -15012,7 +15928,7 @@
       <c r="Y519" s="3"/>
       <c r="Z519" s="3"/>
     </row>
-    <row r="520" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -15040,7 +15956,7 @@
       <c r="Y520" s="3"/>
       <c r="Z520" s="3"/>
     </row>
-    <row r="521" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -15068,7 +15984,7 @@
       <c r="Y521" s="3"/>
       <c r="Z521" s="3"/>
     </row>
-    <row r="522" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -15096,7 +16012,7 @@
       <c r="Y522" s="3"/>
       <c r="Z522" s="3"/>
     </row>
-    <row r="523" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -15124,7 +16040,7 @@
       <c r="Y523" s="3"/>
       <c r="Z523" s="3"/>
     </row>
-    <row r="524" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -15152,7 +16068,7 @@
       <c r="Y524" s="3"/>
       <c r="Z524" s="3"/>
     </row>
-    <row r="525" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -15180,7 +16096,7 @@
       <c r="Y525" s="3"/>
       <c r="Z525" s="3"/>
     </row>
-    <row r="526" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -15208,7 +16124,7 @@
       <c r="Y526" s="3"/>
       <c r="Z526" s="3"/>
     </row>
-    <row r="527" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -15236,7 +16152,7 @@
       <c r="Y527" s="3"/>
       <c r="Z527" s="3"/>
     </row>
-    <row r="528" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -15264,7 +16180,7 @@
       <c r="Y528" s="3"/>
       <c r="Z528" s="3"/>
     </row>
-    <row r="529" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -15292,7 +16208,7 @@
       <c r="Y529" s="3"/>
       <c r="Z529" s="3"/>
     </row>
-    <row r="530" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -15320,7 +16236,7 @@
       <c r="Y530" s="3"/>
       <c r="Z530" s="3"/>
     </row>
-    <row r="531" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -15348,7 +16264,7 @@
       <c r="Y531" s="3"/>
       <c r="Z531" s="3"/>
     </row>
-    <row r="532" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -15376,7 +16292,7 @@
       <c r="Y532" s="3"/>
       <c r="Z532" s="3"/>
     </row>
-    <row r="533" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -15404,7 +16320,7 @@
       <c r="Y533" s="3"/>
       <c r="Z533" s="3"/>
     </row>
-    <row r="534" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -15432,7 +16348,7 @@
       <c r="Y534" s="3"/>
       <c r="Z534" s="3"/>
     </row>
-    <row r="535" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -15460,7 +16376,7 @@
       <c r="Y535" s="3"/>
       <c r="Z535" s="3"/>
     </row>
-    <row r="536" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -15488,7 +16404,7 @@
       <c r="Y536" s="3"/>
       <c r="Z536" s="3"/>
     </row>
-    <row r="537" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -15516,7 +16432,7 @@
       <c r="Y537" s="3"/>
       <c r="Z537" s="3"/>
     </row>
-    <row r="538" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -15544,7 +16460,7 @@
       <c r="Y538" s="3"/>
       <c r="Z538" s="3"/>
     </row>
-    <row r="539" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -15572,7 +16488,7 @@
       <c r="Y539" s="3"/>
       <c r="Z539" s="3"/>
     </row>
-    <row r="540" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -15600,7 +16516,7 @@
       <c r="Y540" s="3"/>
       <c r="Z540" s="3"/>
     </row>
-    <row r="541" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -15628,7 +16544,7 @@
       <c r="Y541" s="3"/>
       <c r="Z541" s="3"/>
     </row>
-    <row r="542" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -15656,7 +16572,7 @@
       <c r="Y542" s="3"/>
       <c r="Z542" s="3"/>
     </row>
-    <row r="543" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -15684,7 +16600,7 @@
       <c r="Y543" s="3"/>
       <c r="Z543" s="3"/>
     </row>
-    <row r="544" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -15712,7 +16628,7 @@
       <c r="Y544" s="3"/>
       <c r="Z544" s="3"/>
     </row>
-    <row r="545" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -15740,7 +16656,7 @@
       <c r="Y545" s="3"/>
       <c r="Z545" s="3"/>
     </row>
-    <row r="546" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -15768,7 +16684,7 @@
       <c r="Y546" s="3"/>
       <c r="Z546" s="3"/>
     </row>
-    <row r="547" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -15796,7 +16712,7 @@
       <c r="Y547" s="3"/>
       <c r="Z547" s="3"/>
     </row>
-    <row r="548" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -15824,7 +16740,7 @@
       <c r="Y548" s="3"/>
       <c r="Z548" s="3"/>
     </row>
-    <row r="549" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -15852,7 +16768,7 @@
       <c r="Y549" s="3"/>
       <c r="Z549" s="3"/>
     </row>
-    <row r="550" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -15880,7 +16796,7 @@
       <c r="Y550" s="3"/>
       <c r="Z550" s="3"/>
     </row>
-    <row r="551" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -15908,7 +16824,7 @@
       <c r="Y551" s="3"/>
       <c r="Z551" s="3"/>
     </row>
-    <row r="552" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -15936,7 +16852,7 @@
       <c r="Y552" s="3"/>
       <c r="Z552" s="3"/>
     </row>
-    <row r="553" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -15964,7 +16880,7 @@
       <c r="Y553" s="3"/>
       <c r="Z553" s="3"/>
     </row>
-    <row r="554" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -15992,7 +16908,7 @@
       <c r="Y554" s="3"/>
       <c r="Z554" s="3"/>
     </row>
-    <row r="555" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -16020,7 +16936,7 @@
       <c r="Y555" s="3"/>
       <c r="Z555" s="3"/>
     </row>
-    <row r="556" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -16048,7 +16964,7 @@
       <c r="Y556" s="3"/>
       <c r="Z556" s="3"/>
     </row>
-    <row r="557" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -16076,7 +16992,7 @@
       <c r="Y557" s="3"/>
       <c r="Z557" s="3"/>
     </row>
-    <row r="558" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -16104,7 +17020,7 @@
       <c r="Y558" s="3"/>
       <c r="Z558" s="3"/>
     </row>
-    <row r="559" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -16132,7 +17048,7 @@
       <c r="Y559" s="3"/>
       <c r="Z559" s="3"/>
     </row>
-    <row r="560" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -16160,7 +17076,7 @@
       <c r="Y560" s="3"/>
       <c r="Z560" s="3"/>
     </row>
-    <row r="561" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -16188,7 +17104,7 @@
       <c r="Y561" s="3"/>
       <c r="Z561" s="3"/>
     </row>
-    <row r="562" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -16216,7 +17132,7 @@
       <c r="Y562" s="3"/>
       <c r="Z562" s="3"/>
     </row>
-    <row r="563" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -16244,7 +17160,7 @@
       <c r="Y563" s="3"/>
       <c r="Z563" s="3"/>
     </row>
-    <row r="564" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -16272,7 +17188,7 @@
       <c r="Y564" s="3"/>
       <c r="Z564" s="3"/>
     </row>
-    <row r="565" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -16300,7 +17216,7 @@
       <c r="Y565" s="3"/>
       <c r="Z565" s="3"/>
     </row>
-    <row r="566" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -16328,7 +17244,7 @@
       <c r="Y566" s="3"/>
       <c r="Z566" s="3"/>
     </row>
-    <row r="567" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -16356,7 +17272,7 @@
       <c r="Y567" s="3"/>
       <c r="Z567" s="3"/>
     </row>
-    <row r="568" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -16384,7 +17300,7 @@
       <c r="Y568" s="3"/>
       <c r="Z568" s="3"/>
     </row>
-    <row r="569" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -16412,7 +17328,7 @@
       <c r="Y569" s="3"/>
       <c r="Z569" s="3"/>
     </row>
-    <row r="570" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -16440,7 +17356,7 @@
       <c r="Y570" s="3"/>
       <c r="Z570" s="3"/>
     </row>
-    <row r="571" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -16468,7 +17384,7 @@
       <c r="Y571" s="3"/>
       <c r="Z571" s="3"/>
     </row>
-    <row r="572" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -16496,7 +17412,7 @@
       <c r="Y572" s="3"/>
       <c r="Z572" s="3"/>
     </row>
-    <row r="573" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -16524,7 +17440,7 @@
       <c r="Y573" s="3"/>
       <c r="Z573" s="3"/>
     </row>
-    <row r="574" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -16552,7 +17468,7 @@
       <c r="Y574" s="3"/>
       <c r="Z574" s="3"/>
     </row>
-    <row r="575" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -16580,7 +17496,7 @@
       <c r="Y575" s="3"/>
       <c r="Z575" s="3"/>
     </row>
-    <row r="576" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -16608,7 +17524,7 @@
       <c r="Y576" s="3"/>
       <c r="Z576" s="3"/>
     </row>
-    <row r="577" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -16636,7 +17552,7 @@
       <c r="Y577" s="3"/>
       <c r="Z577" s="3"/>
     </row>
-    <row r="578" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -16664,7 +17580,7 @@
       <c r="Y578" s="3"/>
       <c r="Z578" s="3"/>
     </row>
-    <row r="579" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -16692,7 +17608,7 @@
       <c r="Y579" s="3"/>
       <c r="Z579" s="3"/>
     </row>
-    <row r="580" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -16720,7 +17636,7 @@
       <c r="Y580" s="3"/>
       <c r="Z580" s="3"/>
     </row>
-    <row r="581" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -16748,7 +17664,7 @@
       <c r="Y581" s="3"/>
       <c r="Z581" s="3"/>
     </row>
-    <row r="582" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -16776,7 +17692,7 @@
       <c r="Y582" s="3"/>
       <c r="Z582" s="3"/>
     </row>
-    <row r="583" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -16804,7 +17720,7 @@
       <c r="Y583" s="3"/>
       <c r="Z583" s="3"/>
     </row>
-    <row r="584" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -16832,7 +17748,7 @@
       <c r="Y584" s="3"/>
       <c r="Z584" s="3"/>
     </row>
-    <row r="585" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -16860,7 +17776,7 @@
       <c r="Y585" s="3"/>
       <c r="Z585" s="3"/>
     </row>
-    <row r="586" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -16888,7 +17804,7 @@
       <c r="Y586" s="3"/>
       <c r="Z586" s="3"/>
     </row>
-    <row r="587" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -16916,7 +17832,7 @@
       <c r="Y587" s="3"/>
       <c r="Z587" s="3"/>
     </row>
-    <row r="588" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -16944,7 +17860,7 @@
       <c r="Y588" s="3"/>
       <c r="Z588" s="3"/>
     </row>
-    <row r="589" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -16972,7 +17888,7 @@
       <c r="Y589" s="3"/>
       <c r="Z589" s="3"/>
     </row>
-    <row r="590" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -17000,7 +17916,7 @@
       <c r="Y590" s="3"/>
       <c r="Z590" s="3"/>
     </row>
-    <row r="591" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -17028,7 +17944,7 @@
       <c r="Y591" s="3"/>
       <c r="Z591" s="3"/>
     </row>
-    <row r="592" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -17056,7 +17972,7 @@
       <c r="Y592" s="3"/>
       <c r="Z592" s="3"/>
     </row>
-    <row r="593" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -17084,7 +18000,7 @@
       <c r="Y593" s="3"/>
       <c r="Z593" s="3"/>
     </row>
-    <row r="594" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -17112,7 +18028,7 @@
       <c r="Y594" s="3"/>
       <c r="Z594" s="3"/>
     </row>
-    <row r="595" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -17140,7 +18056,7 @@
       <c r="Y595" s="3"/>
       <c r="Z595" s="3"/>
     </row>
-    <row r="596" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -17168,7 +18084,7 @@
       <c r="Y596" s="3"/>
       <c r="Z596" s="3"/>
     </row>
-    <row r="597" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -17196,7 +18112,7 @@
       <c r="Y597" s="3"/>
       <c r="Z597" s="3"/>
     </row>
-    <row r="598" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -17224,7 +18140,7 @@
       <c r="Y598" s="3"/>
       <c r="Z598" s="3"/>
     </row>
-    <row r="599" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -17252,7 +18168,7 @@
       <c r="Y599" s="3"/>
       <c r="Z599" s="3"/>
     </row>
-    <row r="600" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -17280,7 +18196,7 @@
       <c r="Y600" s="3"/>
       <c r="Z600" s="3"/>
     </row>
-    <row r="601" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -17308,7 +18224,7 @@
       <c r="Y601" s="3"/>
       <c r="Z601" s="3"/>
     </row>
-    <row r="602" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -17336,7 +18252,7 @@
       <c r="Y602" s="3"/>
       <c r="Z602" s="3"/>
     </row>
-    <row r="603" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -17364,7 +18280,7 @@
       <c r="Y603" s="3"/>
       <c r="Z603" s="3"/>
     </row>
-    <row r="604" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -17392,7 +18308,7 @@
       <c r="Y604" s="3"/>
       <c r="Z604" s="3"/>
     </row>
-    <row r="605" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -17420,7 +18336,7 @@
       <c r="Y605" s="3"/>
       <c r="Z605" s="3"/>
     </row>
-    <row r="606" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -17448,7 +18364,7 @@
       <c r="Y606" s="3"/>
       <c r="Z606" s="3"/>
     </row>
-    <row r="607" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -17476,7 +18392,7 @@
       <c r="Y607" s="3"/>
       <c r="Z607" s="3"/>
     </row>
-    <row r="608" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -17504,7 +18420,7 @@
       <c r="Y608" s="3"/>
       <c r="Z608" s="3"/>
     </row>
-    <row r="609" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -17532,7 +18448,7 @@
       <c r="Y609" s="3"/>
       <c r="Z609" s="3"/>
     </row>
-    <row r="610" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -17560,7 +18476,7 @@
       <c r="Y610" s="3"/>
       <c r="Z610" s="3"/>
     </row>
-    <row r="611" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -17588,7 +18504,7 @@
       <c r="Y611" s="3"/>
       <c r="Z611" s="3"/>
     </row>
-    <row r="612" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -17616,7 +18532,7 @@
       <c r="Y612" s="3"/>
       <c r="Z612" s="3"/>
     </row>
-    <row r="613" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -17644,7 +18560,7 @@
       <c r="Y613" s="3"/>
       <c r="Z613" s="3"/>
     </row>
-    <row r="614" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -17672,7 +18588,7 @@
       <c r="Y614" s="3"/>
       <c r="Z614" s="3"/>
     </row>
-    <row r="615" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -17700,7 +18616,7 @@
       <c r="Y615" s="3"/>
       <c r="Z615" s="3"/>
     </row>
-    <row r="616" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -17728,7 +18644,7 @@
       <c r="Y616" s="3"/>
       <c r="Z616" s="3"/>
     </row>
-    <row r="617" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -17756,7 +18672,7 @@
       <c r="Y617" s="3"/>
       <c r="Z617" s="3"/>
     </row>
-    <row r="618" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -17784,7 +18700,7 @@
       <c r="Y618" s="3"/>
       <c r="Z618" s="3"/>
     </row>
-    <row r="619" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -17812,7 +18728,7 @@
       <c r="Y619" s="3"/>
       <c r="Z619" s="3"/>
     </row>
-    <row r="620" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -17840,7 +18756,7 @@
       <c r="Y620" s="3"/>
       <c r="Z620" s="3"/>
     </row>
-    <row r="621" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -17868,7 +18784,7 @@
       <c r="Y621" s="3"/>
       <c r="Z621" s="3"/>
     </row>
-    <row r="622" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -17896,7 +18812,7 @@
       <c r="Y622" s="3"/>
       <c r="Z622" s="3"/>
     </row>
-    <row r="623" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -17924,7 +18840,7 @@
       <c r="Y623" s="3"/>
       <c r="Z623" s="3"/>
     </row>
-    <row r="624" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -17952,7 +18868,7 @@
       <c r="Y624" s="3"/>
       <c r="Z624" s="3"/>
     </row>
-    <row r="625" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -17980,7 +18896,7 @@
       <c r="Y625" s="3"/>
       <c r="Z625" s="3"/>
     </row>
-    <row r="626" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -18008,7 +18924,7 @@
       <c r="Y626" s="3"/>
       <c r="Z626" s="3"/>
     </row>
-    <row r="627" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -18036,7 +18952,7 @@
       <c r="Y627" s="3"/>
       <c r="Z627" s="3"/>
     </row>
-    <row r="628" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -18064,7 +18980,7 @@
       <c r="Y628" s="3"/>
       <c r="Z628" s="3"/>
     </row>
-    <row r="629" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -18092,7 +19008,7 @@
       <c r="Y629" s="3"/>
       <c r="Z629" s="3"/>
     </row>
-    <row r="630" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -18120,7 +19036,7 @@
       <c r="Y630" s="3"/>
       <c r="Z630" s="3"/>
     </row>
-    <row r="631" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -18148,7 +19064,7 @@
       <c r="Y631" s="3"/>
       <c r="Z631" s="3"/>
     </row>
-    <row r="632" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -18176,7 +19092,7 @@
       <c r="Y632" s="3"/>
       <c r="Z632" s="3"/>
     </row>
-    <row r="633" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -18204,7 +19120,7 @@
       <c r="Y633" s="3"/>
       <c r="Z633" s="3"/>
     </row>
-    <row r="634" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -18232,7 +19148,7 @@
       <c r="Y634" s="3"/>
       <c r="Z634" s="3"/>
     </row>
-    <row r="635" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -18260,7 +19176,7 @@
       <c r="Y635" s="3"/>
       <c r="Z635" s="3"/>
     </row>
-    <row r="636" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -18288,7 +19204,7 @@
       <c r="Y636" s="3"/>
       <c r="Z636" s="3"/>
     </row>
-    <row r="637" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -18316,7 +19232,7 @@
       <c r="Y637" s="3"/>
       <c r="Z637" s="3"/>
     </row>
-    <row r="638" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -18344,7 +19260,7 @@
       <c r="Y638" s="3"/>
       <c r="Z638" s="3"/>
     </row>
-    <row r="639" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -18372,7 +19288,7 @@
       <c r="Y639" s="3"/>
       <c r="Z639" s="3"/>
     </row>
-    <row r="640" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -18400,7 +19316,7 @@
       <c r="Y640" s="3"/>
       <c r="Z640" s="3"/>
     </row>
-    <row r="641" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -18428,7 +19344,7 @@
       <c r="Y641" s="3"/>
       <c r="Z641" s="3"/>
     </row>
-    <row r="642" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -18456,7 +19372,7 @@
       <c r="Y642" s="3"/>
       <c r="Z642" s="3"/>
     </row>
-    <row r="643" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -18484,7 +19400,7 @@
       <c r="Y643" s="3"/>
       <c r="Z643" s="3"/>
     </row>
-    <row r="644" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -18512,7 +19428,7 @@
       <c r="Y644" s="3"/>
       <c r="Z644" s="3"/>
     </row>
-    <row r="645" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -18540,7 +19456,7 @@
       <c r="Y645" s="3"/>
       <c r="Z645" s="3"/>
     </row>
-    <row r="646" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -18568,7 +19484,7 @@
       <c r="Y646" s="3"/>
       <c r="Z646" s="3"/>
     </row>
-    <row r="647" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -18596,7 +19512,7 @@
       <c r="Y647" s="3"/>
       <c r="Z647" s="3"/>
     </row>
-    <row r="648" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -18624,7 +19540,7 @@
       <c r="Y648" s="3"/>
       <c r="Z648" s="3"/>
     </row>
-    <row r="649" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -18652,7 +19568,7 @@
       <c r="Y649" s="3"/>
       <c r="Z649" s="3"/>
     </row>
-    <row r="650" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -18680,7 +19596,7 @@
       <c r="Y650" s="3"/>
       <c r="Z650" s="3"/>
     </row>
-    <row r="651" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -18708,7 +19624,7 @@
       <c r="Y651" s="3"/>
       <c r="Z651" s="3"/>
     </row>
-    <row r="652" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -18736,7 +19652,7 @@
       <c r="Y652" s="3"/>
       <c r="Z652" s="3"/>
     </row>
-    <row r="653" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -18764,7 +19680,7 @@
       <c r="Y653" s="3"/>
       <c r="Z653" s="3"/>
     </row>
-    <row r="654" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -18792,7 +19708,7 @@
       <c r="Y654" s="3"/>
       <c r="Z654" s="3"/>
     </row>
-    <row r="655" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -18820,7 +19736,7 @@
       <c r="Y655" s="3"/>
       <c r="Z655" s="3"/>
     </row>
-    <row r="656" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -18848,7 +19764,7 @@
       <c r="Y656" s="3"/>
       <c r="Z656" s="3"/>
     </row>
-    <row r="657" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -18876,7 +19792,7 @@
       <c r="Y657" s="3"/>
       <c r="Z657" s="3"/>
     </row>
-    <row r="658" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -18904,7 +19820,7 @@
       <c r="Y658" s="3"/>
       <c r="Z658" s="3"/>
     </row>
-    <row r="659" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -18932,7 +19848,7 @@
       <c r="Y659" s="3"/>
       <c r="Z659" s="3"/>
     </row>
-    <row r="660" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -18960,7 +19876,7 @@
       <c r="Y660" s="3"/>
       <c r="Z660" s="3"/>
     </row>
-    <row r="661" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -18988,7 +19904,7 @@
       <c r="Y661" s="3"/>
       <c r="Z661" s="3"/>
     </row>
-    <row r="662" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -19016,7 +19932,7 @@
       <c r="Y662" s="3"/>
       <c r="Z662" s="3"/>
     </row>
-    <row r="663" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -19044,7 +19960,7 @@
       <c r="Y663" s="3"/>
       <c r="Z663" s="3"/>
     </row>
-    <row r="664" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -19072,7 +19988,7 @@
       <c r="Y664" s="3"/>
       <c r="Z664" s="3"/>
     </row>
-    <row r="665" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -19100,7 +20016,7 @@
       <c r="Y665" s="3"/>
       <c r="Z665" s="3"/>
     </row>
-    <row r="666" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -19128,7 +20044,7 @@
       <c r="Y666" s="3"/>
       <c r="Z666" s="3"/>
     </row>
-    <row r="667" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -19156,7 +20072,7 @@
       <c r="Y667" s="3"/>
       <c r="Z667" s="3"/>
     </row>
-    <row r="668" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -19184,7 +20100,7 @@
       <c r="Y668" s="3"/>
       <c r="Z668" s="3"/>
     </row>
-    <row r="669" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -19212,7 +20128,7 @@
       <c r="Y669" s="3"/>
       <c r="Z669" s="3"/>
     </row>
-    <row r="670" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -19240,7 +20156,7 @@
       <c r="Y670" s="3"/>
       <c r="Z670" s="3"/>
     </row>
-    <row r="671" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -19268,7 +20184,7 @@
       <c r="Y671" s="3"/>
       <c r="Z671" s="3"/>
     </row>
-    <row r="672" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -19296,7 +20212,7 @@
       <c r="Y672" s="3"/>
       <c r="Z672" s="3"/>
     </row>
-    <row r="673" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -19324,7 +20240,7 @@
       <c r="Y673" s="3"/>
       <c r="Z673" s="3"/>
     </row>
-    <row r="674" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -19352,7 +20268,7 @@
       <c r="Y674" s="3"/>
       <c r="Z674" s="3"/>
     </row>
-    <row r="675" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -19380,7 +20296,7 @@
       <c r="Y675" s="3"/>
       <c r="Z675" s="3"/>
     </row>
-    <row r="676" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -19408,7 +20324,7 @@
       <c r="Y676" s="3"/>
       <c r="Z676" s="3"/>
     </row>
-    <row r="677" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -19436,7 +20352,7 @@
       <c r="Y677" s="3"/>
       <c r="Z677" s="3"/>
     </row>
-    <row r="678" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -19464,7 +20380,7 @@
       <c r="Y678" s="3"/>
       <c r="Z678" s="3"/>
     </row>
-    <row r="679" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -19492,7 +20408,7 @@
       <c r="Y679" s="3"/>
       <c r="Z679" s="3"/>
     </row>
-    <row r="680" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -19520,7 +20436,7 @@
       <c r="Y680" s="3"/>
       <c r="Z680" s="3"/>
     </row>
-    <row r="681" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -19548,7 +20464,7 @@
       <c r="Y681" s="3"/>
       <c r="Z681" s="3"/>
     </row>
-    <row r="682" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -19576,7 +20492,7 @@
       <c r="Y682" s="3"/>
       <c r="Z682" s="3"/>
     </row>
-    <row r="683" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -19604,7 +20520,7 @@
       <c r="Y683" s="3"/>
       <c r="Z683" s="3"/>
     </row>
-    <row r="684" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -19632,7 +20548,7 @@
       <c r="Y684" s="3"/>
       <c r="Z684" s="3"/>
     </row>
-    <row r="685" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -19660,7 +20576,7 @@
       <c r="Y685" s="3"/>
       <c r="Z685" s="3"/>
     </row>
-    <row r="686" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -19688,7 +20604,7 @@
       <c r="Y686" s="3"/>
       <c r="Z686" s="3"/>
     </row>
-    <row r="687" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -19716,7 +20632,7 @@
       <c r="Y687" s="3"/>
       <c r="Z687" s="3"/>
     </row>
-    <row r="688" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -19744,7 +20660,7 @@
       <c r="Y688" s="3"/>
       <c r="Z688" s="3"/>
     </row>
-    <row r="689" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -19772,7 +20688,7 @@
       <c r="Y689" s="3"/>
       <c r="Z689" s="3"/>
     </row>
-    <row r="690" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -19800,7 +20716,7 @@
       <c r="Y690" s="3"/>
       <c r="Z690" s="3"/>
     </row>
-    <row r="691" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -19828,7 +20744,7 @@
       <c r="Y691" s="3"/>
       <c r="Z691" s="3"/>
     </row>
-    <row r="692" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -19856,7 +20772,7 @@
       <c r="Y692" s="3"/>
       <c r="Z692" s="3"/>
     </row>
-    <row r="693" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -19884,7 +20800,7 @@
       <c r="Y693" s="3"/>
       <c r="Z693" s="3"/>
     </row>
-    <row r="694" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -19912,7 +20828,7 @@
       <c r="Y694" s="3"/>
       <c r="Z694" s="3"/>
     </row>
-    <row r="695" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -19940,7 +20856,7 @@
       <c r="Y695" s="3"/>
       <c r="Z695" s="3"/>
     </row>
-    <row r="696" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -19968,7 +20884,7 @@
       <c r="Y696" s="3"/>
       <c r="Z696" s="3"/>
     </row>
-    <row r="697" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -19996,7 +20912,7 @@
       <c r="Y697" s="3"/>
       <c r="Z697" s="3"/>
     </row>
-    <row r="698" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -20024,7 +20940,7 @@
       <c r="Y698" s="3"/>
       <c r="Z698" s="3"/>
     </row>
-    <row r="699" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -20052,7 +20968,7 @@
       <c r="Y699" s="3"/>
       <c r="Z699" s="3"/>
     </row>
-    <row r="700" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -20080,7 +20996,7 @@
       <c r="Y700" s="3"/>
       <c r="Z700" s="3"/>
     </row>
-    <row r="701" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -20108,7 +21024,7 @@
       <c r="Y701" s="3"/>
       <c r="Z701" s="3"/>
     </row>
-    <row r="702" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -20136,7 +21052,7 @@
       <c r="Y702" s="3"/>
       <c r="Z702" s="3"/>
     </row>
-    <row r="703" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -20164,7 +21080,7 @@
       <c r="Y703" s="3"/>
       <c r="Z703" s="3"/>
     </row>
-    <row r="704" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -20192,7 +21108,7 @@
       <c r="Y704" s="3"/>
       <c r="Z704" s="3"/>
     </row>
-    <row r="705" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -20220,7 +21136,7 @@
       <c r="Y705" s="3"/>
       <c r="Z705" s="3"/>
     </row>
-    <row r="706" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -20248,7 +21164,7 @@
       <c r="Y706" s="3"/>
       <c r="Z706" s="3"/>
     </row>
-    <row r="707" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -20276,7 +21192,7 @@
       <c r="Y707" s="3"/>
       <c r="Z707" s="3"/>
     </row>
-    <row r="708" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -20304,7 +21220,7 @@
       <c r="Y708" s="3"/>
       <c r="Z708" s="3"/>
     </row>
-    <row r="709" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -20332,7 +21248,7 @@
       <c r="Y709" s="3"/>
       <c r="Z709" s="3"/>
     </row>
-    <row r="710" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -20360,7 +21276,7 @@
       <c r="Y710" s="3"/>
       <c r="Z710" s="3"/>
     </row>
-    <row r="711" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -20388,7 +21304,7 @@
       <c r="Y711" s="3"/>
       <c r="Z711" s="3"/>
     </row>
-    <row r="712" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -20416,7 +21332,7 @@
       <c r="Y712" s="3"/>
       <c r="Z712" s="3"/>
     </row>
-    <row r="713" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -20444,7 +21360,7 @@
       <c r="Y713" s="3"/>
       <c r="Z713" s="3"/>
     </row>
-    <row r="714" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -20472,7 +21388,7 @@
       <c r="Y714" s="3"/>
       <c r="Z714" s="3"/>
     </row>
-    <row r="715" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -20500,7 +21416,7 @@
       <c r="Y715" s="3"/>
       <c r="Z715" s="3"/>
     </row>
-    <row r="716" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -20528,7 +21444,7 @@
       <c r="Y716" s="3"/>
       <c r="Z716" s="3"/>
     </row>
-    <row r="717" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -20556,7 +21472,7 @@
       <c r="Y717" s="3"/>
       <c r="Z717" s="3"/>
     </row>
-    <row r="718" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -20584,7 +21500,7 @@
       <c r="Y718" s="3"/>
       <c r="Z718" s="3"/>
     </row>
-    <row r="719" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -20612,7 +21528,7 @@
       <c r="Y719" s="3"/>
       <c r="Z719" s="3"/>
     </row>
-    <row r="720" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -20640,7 +21556,7 @@
       <c r="Y720" s="3"/>
       <c r="Z720" s="3"/>
     </row>
-    <row r="721" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -20668,7 +21584,7 @@
       <c r="Y721" s="3"/>
       <c r="Z721" s="3"/>
     </row>
-    <row r="722" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -20696,7 +21612,7 @@
       <c r="Y722" s="3"/>
       <c r="Z722" s="3"/>
     </row>
-    <row r="723" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -20724,7 +21640,7 @@
       <c r="Y723" s="3"/>
       <c r="Z723" s="3"/>
     </row>
-    <row r="724" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -20752,7 +21668,7 @@
       <c r="Y724" s="3"/>
       <c r="Z724" s="3"/>
     </row>
-    <row r="725" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -20780,7 +21696,7 @@
       <c r="Y725" s="3"/>
       <c r="Z725" s="3"/>
     </row>
-    <row r="726" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -20808,7 +21724,7 @@
       <c r="Y726" s="3"/>
       <c r="Z726" s="3"/>
     </row>
-    <row r="727" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -20836,7 +21752,7 @@
       <c r="Y727" s="3"/>
       <c r="Z727" s="3"/>
     </row>
-    <row r="728" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -20864,7 +21780,7 @@
       <c r="Y728" s="3"/>
       <c r="Z728" s="3"/>
     </row>
-    <row r="729" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -20892,7 +21808,7 @@
       <c r="Y729" s="3"/>
       <c r="Z729" s="3"/>
     </row>
-    <row r="730" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -20920,7 +21836,7 @@
       <c r="Y730" s="3"/>
       <c r="Z730" s="3"/>
     </row>
-    <row r="731" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -20948,7 +21864,7 @@
       <c r="Y731" s="3"/>
       <c r="Z731" s="3"/>
     </row>
-    <row r="732" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -20976,7 +21892,7 @@
       <c r="Y732" s="3"/>
       <c r="Z732" s="3"/>
     </row>
-    <row r="733" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -21004,7 +21920,7 @@
       <c r="Y733" s="3"/>
       <c r="Z733" s="3"/>
     </row>
-    <row r="734" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -21032,7 +21948,7 @@
       <c r="Y734" s="3"/>
       <c r="Z734" s="3"/>
     </row>
-    <row r="735" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -21060,7 +21976,7 @@
       <c r="Y735" s="3"/>
       <c r="Z735" s="3"/>
     </row>
-    <row r="736" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -21088,7 +22004,7 @@
       <c r="Y736" s="3"/>
       <c r="Z736" s="3"/>
     </row>
-    <row r="737" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -21116,7 +22032,7 @@
       <c r="Y737" s="3"/>
       <c r="Z737" s="3"/>
     </row>
-    <row r="738" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -21144,7 +22060,7 @@
       <c r="Y738" s="3"/>
       <c r="Z738" s="3"/>
     </row>
-    <row r="739" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -21172,7 +22088,7 @@
       <c r="Y739" s="3"/>
       <c r="Z739" s="3"/>
     </row>
-    <row r="740" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -21200,7 +22116,7 @@
       <c r="Y740" s="3"/>
       <c r="Z740" s="3"/>
     </row>
-    <row r="741" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -21228,7 +22144,7 @@
       <c r="Y741" s="3"/>
       <c r="Z741" s="3"/>
     </row>
-    <row r="742" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -21256,7 +22172,7 @@
       <c r="Y742" s="3"/>
       <c r="Z742" s="3"/>
     </row>
-    <row r="743" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -21284,7 +22200,7 @@
       <c r="Y743" s="3"/>
       <c r="Z743" s="3"/>
     </row>
-    <row r="744" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -21312,7 +22228,7 @@
       <c r="Y744" s="3"/>
       <c r="Z744" s="3"/>
     </row>
-    <row r="745" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -21340,7 +22256,7 @@
       <c r="Y745" s="3"/>
       <c r="Z745" s="3"/>
     </row>
-    <row r="746" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -21368,7 +22284,7 @@
       <c r="Y746" s="3"/>
       <c r="Z746" s="3"/>
     </row>
-    <row r="747" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -21396,7 +22312,7 @@
       <c r="Y747" s="3"/>
       <c r="Z747" s="3"/>
     </row>
-    <row r="748" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -21424,7 +22340,7 @@
       <c r="Y748" s="3"/>
       <c r="Z748" s="3"/>
     </row>
-    <row r="749" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -21452,7 +22368,7 @@
       <c r="Y749" s="3"/>
       <c r="Z749" s="3"/>
     </row>
-    <row r="750" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -21480,7 +22396,7 @@
       <c r="Y750" s="3"/>
       <c r="Z750" s="3"/>
     </row>
-    <row r="751" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -21508,7 +22424,7 @@
       <c r="Y751" s="3"/>
       <c r="Z751" s="3"/>
     </row>
-    <row r="752" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -21536,7 +22452,7 @@
       <c r="Y752" s="3"/>
       <c r="Z752" s="3"/>
     </row>
-    <row r="753" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -21564,7 +22480,7 @@
       <c r="Y753" s="3"/>
       <c r="Z753" s="3"/>
     </row>
-    <row r="754" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -21592,7 +22508,7 @@
       <c r="Y754" s="3"/>
       <c r="Z754" s="3"/>
     </row>
-    <row r="755" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -21620,7 +22536,7 @@
       <c r="Y755" s="3"/>
       <c r="Z755" s="3"/>
     </row>
-    <row r="756" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -21648,7 +22564,7 @@
       <c r="Y756" s="3"/>
       <c r="Z756" s="3"/>
     </row>
-    <row r="757" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -21676,7 +22592,7 @@
       <c r="Y757" s="3"/>
       <c r="Z757" s="3"/>
     </row>
-    <row r="758" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -21704,7 +22620,7 @@
       <c r="Y758" s="3"/>
       <c r="Z758" s="3"/>
     </row>
-    <row r="759" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -21732,7 +22648,7 @@
       <c r="Y759" s="3"/>
       <c r="Z759" s="3"/>
     </row>
-    <row r="760" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -21760,7 +22676,7 @@
       <c r="Y760" s="3"/>
       <c r="Z760" s="3"/>
     </row>
-    <row r="761" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -21788,7 +22704,7 @@
       <c r="Y761" s="3"/>
       <c r="Z761" s="3"/>
     </row>
-    <row r="762" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -21816,7 +22732,7 @@
       <c r="Y762" s="3"/>
       <c r="Z762" s="3"/>
     </row>
-    <row r="763" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -21844,7 +22760,7 @@
       <c r="Y763" s="3"/>
       <c r="Z763" s="3"/>
     </row>
-    <row r="764" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -21872,7 +22788,7 @@
       <c r="Y764" s="3"/>
       <c r="Z764" s="3"/>
     </row>
-    <row r="765" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -21900,7 +22816,7 @@
       <c r="Y765" s="3"/>
       <c r="Z765" s="3"/>
     </row>
-    <row r="766" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -21928,7 +22844,7 @@
       <c r="Y766" s="3"/>
       <c r="Z766" s="3"/>
     </row>
-    <row r="767" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -21956,7 +22872,7 @@
       <c r="Y767" s="3"/>
       <c r="Z767" s="3"/>
     </row>
-    <row r="768" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -21984,7 +22900,7 @@
       <c r="Y768" s="3"/>
       <c r="Z768" s="3"/>
     </row>
-    <row r="769" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -22012,7 +22928,7 @@
       <c r="Y769" s="3"/>
       <c r="Z769" s="3"/>
     </row>
-    <row r="770" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -22040,7 +22956,7 @@
       <c r="Y770" s="3"/>
       <c r="Z770" s="3"/>
     </row>
-    <row r="771" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -22068,7 +22984,7 @@
       <c r="Y771" s="3"/>
       <c r="Z771" s="3"/>
     </row>
-    <row r="772" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -22096,7 +23012,7 @@
       <c r="Y772" s="3"/>
       <c r="Z772" s="3"/>
     </row>
-    <row r="773" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -22124,7 +23040,7 @@
       <c r="Y773" s="3"/>
       <c r="Z773" s="3"/>
     </row>
-    <row r="774" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -22152,7 +23068,7 @@
       <c r="Y774" s="3"/>
       <c r="Z774" s="3"/>
     </row>
-    <row r="775" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -22180,7 +23096,7 @@
       <c r="Y775" s="3"/>
       <c r="Z775" s="3"/>
     </row>
-    <row r="776" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -22208,7 +23124,7 @@
       <c r="Y776" s="3"/>
       <c r="Z776" s="3"/>
     </row>
-    <row r="777" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -22236,7 +23152,7 @@
       <c r="Y777" s="3"/>
       <c r="Z777" s="3"/>
     </row>
-    <row r="778" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -22264,7 +23180,7 @@
       <c r="Y778" s="3"/>
       <c r="Z778" s="3"/>
     </row>
-    <row r="779" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -22292,7 +23208,7 @@
       <c r="Y779" s="3"/>
       <c r="Z779" s="3"/>
     </row>
-    <row r="780" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -22320,7 +23236,7 @@
       <c r="Y780" s="3"/>
       <c r="Z780" s="3"/>
     </row>
-    <row r="781" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -22348,7 +23264,7 @@
       <c r="Y781" s="3"/>
       <c r="Z781" s="3"/>
     </row>
-    <row r="782" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -22376,7 +23292,7 @@
       <c r="Y782" s="3"/>
       <c r="Z782" s="3"/>
     </row>
-    <row r="783" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -22404,7 +23320,7 @@
       <c r="Y783" s="3"/>
       <c r="Z783" s="3"/>
     </row>
-    <row r="784" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -22432,7 +23348,7 @@
       <c r="Y784" s="3"/>
       <c r="Z784" s="3"/>
     </row>
-    <row r="785" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -22460,7 +23376,7 @@
       <c r="Y785" s="3"/>
       <c r="Z785" s="3"/>
     </row>
-    <row r="786" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -22488,7 +23404,7 @@
       <c r="Y786" s="3"/>
       <c r="Z786" s="3"/>
     </row>
-    <row r="787" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -22516,7 +23432,7 @@
       <c r="Y787" s="3"/>
       <c r="Z787" s="3"/>
     </row>
-    <row r="788" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -22544,7 +23460,7 @@
       <c r="Y788" s="3"/>
       <c r="Z788" s="3"/>
     </row>
-    <row r="789" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -22572,7 +23488,7 @@
       <c r="Y789" s="3"/>
       <c r="Z789" s="3"/>
     </row>
-    <row r="790" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -22600,7 +23516,7 @@
       <c r="Y790" s="3"/>
       <c r="Z790" s="3"/>
     </row>
-    <row r="791" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -22628,7 +23544,7 @@
       <c r="Y791" s="3"/>
       <c r="Z791" s="3"/>
     </row>
-    <row r="792" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -22656,7 +23572,7 @@
       <c r="Y792" s="3"/>
       <c r="Z792" s="3"/>
     </row>
-    <row r="793" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -22684,7 +23600,7 @@
       <c r="Y793" s="3"/>
       <c r="Z793" s="3"/>
     </row>
-    <row r="794" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -22712,7 +23628,7 @@
       <c r="Y794" s="3"/>
       <c r="Z794" s="3"/>
     </row>
-    <row r="795" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -22740,7 +23656,7 @@
       <c r="Y795" s="3"/>
       <c r="Z795" s="3"/>
     </row>
-    <row r="796" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -22768,7 +23684,7 @@
       <c r="Y796" s="3"/>
       <c r="Z796" s="3"/>
     </row>
-    <row r="797" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -22796,7 +23712,7 @@
       <c r="Y797" s="3"/>
       <c r="Z797" s="3"/>
     </row>
-    <row r="798" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -22824,7 +23740,7 @@
       <c r="Y798" s="3"/>
       <c r="Z798" s="3"/>
     </row>
-    <row r="799" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -22852,7 +23768,7 @@
       <c r="Y799" s="3"/>
       <c r="Z799" s="3"/>
     </row>
-    <row r="800" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -22880,7 +23796,7 @@
       <c r="Y800" s="3"/>
       <c r="Z800" s="3"/>
     </row>
-    <row r="801" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -22908,7 +23824,7 @@
       <c r="Y801" s="3"/>
       <c r="Z801" s="3"/>
     </row>
-    <row r="802" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -22936,7 +23852,7 @@
       <c r="Y802" s="3"/>
       <c r="Z802" s="3"/>
     </row>
-    <row r="803" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -22964,7 +23880,7 @@
       <c r="Y803" s="3"/>
       <c r="Z803" s="3"/>
     </row>
-    <row r="804" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -22992,7 +23908,7 @@
       <c r="Y804" s="3"/>
       <c r="Z804" s="3"/>
     </row>
-    <row r="805" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -23020,7 +23936,7 @@
       <c r="Y805" s="3"/>
       <c r="Z805" s="3"/>
     </row>
-    <row r="806" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -23048,7 +23964,7 @@
       <c r="Y806" s="3"/>
       <c r="Z806" s="3"/>
     </row>
-    <row r="807" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -23076,7 +23992,7 @@
       <c r="Y807" s="3"/>
       <c r="Z807" s="3"/>
     </row>
-    <row r="808" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -23104,7 +24020,7 @@
       <c r="Y808" s="3"/>
       <c r="Z808" s="3"/>
     </row>
-    <row r="809" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -23132,7 +24048,7 @@
       <c r="Y809" s="3"/>
       <c r="Z809" s="3"/>
     </row>
-    <row r="810" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -23160,7 +24076,7 @@
       <c r="Y810" s="3"/>
       <c r="Z810" s="3"/>
     </row>
-    <row r="811" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -23188,7 +24104,7 @@
       <c r="Y811" s="3"/>
       <c r="Z811" s="3"/>
     </row>
-    <row r="812" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -23216,7 +24132,7 @@
       <c r="Y812" s="3"/>
       <c r="Z812" s="3"/>
     </row>
-    <row r="813" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -23244,7 +24160,7 @@
       <c r="Y813" s="3"/>
       <c r="Z813" s="3"/>
     </row>
-    <row r="814" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -23272,7 +24188,7 @@
       <c r="Y814" s="3"/>
       <c r="Z814" s="3"/>
     </row>
-    <row r="815" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -23300,7 +24216,7 @@
       <c r="Y815" s="3"/>
       <c r="Z815" s="3"/>
     </row>
-    <row r="816" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -23328,7 +24244,7 @@
       <c r="Y816" s="3"/>
       <c r="Z816" s="3"/>
     </row>
-    <row r="817" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -23356,7 +24272,7 @@
       <c r="Y817" s="3"/>
       <c r="Z817" s="3"/>
     </row>
-    <row r="818" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -23384,7 +24300,7 @@
       <c r="Y818" s="3"/>
       <c r="Z818" s="3"/>
     </row>
-    <row r="819" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -23412,7 +24328,7 @@
       <c r="Y819" s="3"/>
       <c r="Z819" s="3"/>
     </row>
-    <row r="820" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -23440,7 +24356,7 @@
       <c r="Y820" s="3"/>
       <c r="Z820" s="3"/>
     </row>
-    <row r="821" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -23468,7 +24384,7 @@
       <c r="Y821" s="3"/>
       <c r="Z821" s="3"/>
     </row>
-    <row r="822" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -23496,7 +24412,7 @@
       <c r="Y822" s="3"/>
       <c r="Z822" s="3"/>
     </row>
-    <row r="823" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -23524,7 +24440,7 @@
       <c r="Y823" s="3"/>
       <c r="Z823" s="3"/>
     </row>
-    <row r="824" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -23552,7 +24468,7 @@
       <c r="Y824" s="3"/>
       <c r="Z824" s="3"/>
     </row>
-    <row r="825" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -23580,7 +24496,7 @@
       <c r="Y825" s="3"/>
       <c r="Z825" s="3"/>
     </row>
-    <row r="826" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -23608,7 +24524,7 @@
       <c r="Y826" s="3"/>
       <c r="Z826" s="3"/>
     </row>
-    <row r="827" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -23636,7 +24552,7 @@
       <c r="Y827" s="3"/>
       <c r="Z827" s="3"/>
     </row>
-    <row r="828" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -23664,7 +24580,7 @@
       <c r="Y828" s="3"/>
       <c r="Z828" s="3"/>
     </row>
-    <row r="829" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -23692,7 +24608,7 @@
       <c r="Y829" s="3"/>
       <c r="Z829" s="3"/>
     </row>
-    <row r="830" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -23720,7 +24636,7 @@
       <c r="Y830" s="3"/>
       <c r="Z830" s="3"/>
     </row>
-    <row r="831" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -23748,7 +24664,7 @@
       <c r="Y831" s="3"/>
       <c r="Z831" s="3"/>
     </row>
-    <row r="832" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -23776,7 +24692,7 @@
       <c r="Y832" s="3"/>
       <c r="Z832" s="3"/>
     </row>
-    <row r="833" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -23804,7 +24720,7 @@
       <c r="Y833" s="3"/>
       <c r="Z833" s="3"/>
     </row>
-    <row r="834" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -23832,7 +24748,7 @@
       <c r="Y834" s="3"/>
       <c r="Z834" s="3"/>
     </row>
-    <row r="835" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -23860,7 +24776,7 @@
       <c r="Y835" s="3"/>
       <c r="Z835" s="3"/>
     </row>
-    <row r="836" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -23888,7 +24804,7 @@
       <c r="Y836" s="3"/>
       <c r="Z836" s="3"/>
     </row>
-    <row r="837" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -23916,7 +24832,7 @@
       <c r="Y837" s="3"/>
       <c r="Z837" s="3"/>
     </row>
-    <row r="838" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -23944,7 +24860,7 @@
       <c r="Y838" s="3"/>
       <c r="Z838" s="3"/>
     </row>
-    <row r="839" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -23972,7 +24888,7 @@
       <c r="Y839" s="3"/>
       <c r="Z839" s="3"/>
     </row>
-    <row r="840" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -24000,7 +24916,7 @@
       <c r="Y840" s="3"/>
       <c r="Z840" s="3"/>
     </row>
-    <row r="841" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -24028,7 +24944,7 @@
       <c r="Y841" s="3"/>
       <c r="Z841" s="3"/>
     </row>
-    <row r="842" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -24056,7 +24972,7 @@
       <c r="Y842" s="3"/>
       <c r="Z842" s="3"/>
     </row>
-    <row r="843" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -24084,7 +25000,7 @@
       <c r="Y843" s="3"/>
       <c r="Z843" s="3"/>
     </row>
-    <row r="844" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -24112,7 +25028,7 @@
       <c r="Y844" s="3"/>
       <c r="Z844" s="3"/>
     </row>
-    <row r="845" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -24140,7 +25056,7 @@
       <c r="Y845" s="3"/>
       <c r="Z845" s="3"/>
     </row>
-    <row r="846" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -24168,7 +25084,7 @@
       <c r="Y846" s="3"/>
       <c r="Z846" s="3"/>
     </row>
-    <row r="847" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -24196,7 +25112,7 @@
       <c r="Y847" s="3"/>
       <c r="Z847" s="3"/>
     </row>
-    <row r="848" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -24224,7 +25140,7 @@
       <c r="Y848" s="3"/>
       <c r="Z848" s="3"/>
     </row>
-    <row r="849" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -24252,7 +25168,7 @@
       <c r="Y849" s="3"/>
       <c r="Z849" s="3"/>
     </row>
-    <row r="850" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -24280,7 +25196,7 @@
       <c r="Y850" s="3"/>
       <c r="Z850" s="3"/>
     </row>
-    <row r="851" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -24308,7 +25224,7 @@
       <c r="Y851" s="3"/>
       <c r="Z851" s="3"/>
     </row>
-    <row r="852" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -24336,7 +25252,7 @@
       <c r="Y852" s="3"/>
       <c r="Z852" s="3"/>
     </row>
-    <row r="853" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -24364,7 +25280,7 @@
       <c r="Y853" s="3"/>
       <c r="Z853" s="3"/>
     </row>
-    <row r="854" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -24392,7 +25308,7 @@
       <c r="Y854" s="3"/>
       <c r="Z854" s="3"/>
     </row>
-    <row r="855" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -24420,7 +25336,7 @@
       <c r="Y855" s="3"/>
       <c r="Z855" s="3"/>
     </row>
-    <row r="856" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -24448,7 +25364,7 @@
       <c r="Y856" s="3"/>
       <c r="Z856" s="3"/>
     </row>
-    <row r="857" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -24476,7 +25392,7 @@
       <c r="Y857" s="3"/>
       <c r="Z857" s="3"/>
     </row>
-    <row r="858" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -24504,7 +25420,7 @@
       <c r="Y858" s="3"/>
       <c r="Z858" s="3"/>
     </row>
-    <row r="859" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -24532,7 +25448,7 @@
       <c r="Y859" s="3"/>
       <c r="Z859" s="3"/>
     </row>
-    <row r="860" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -24560,7 +25476,7 @@
       <c r="Y860" s="3"/>
       <c r="Z860" s="3"/>
     </row>
-    <row r="861" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -24588,7 +25504,7 @@
       <c r="Y861" s="3"/>
       <c r="Z861" s="3"/>
     </row>
-    <row r="862" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -24616,7 +25532,7 @@
       <c r="Y862" s="3"/>
       <c r="Z862" s="3"/>
     </row>
-    <row r="863" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -24644,7 +25560,7 @@
       <c r="Y863" s="3"/>
       <c r="Z863" s="3"/>
     </row>
-    <row r="864" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -24672,7 +25588,7 @@
       <c r="Y864" s="3"/>
       <c r="Z864" s="3"/>
     </row>
-    <row r="865" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -24700,7 +25616,7 @@
       <c r="Y865" s="3"/>
       <c r="Z865" s="3"/>
     </row>
-    <row r="866" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -24728,7 +25644,7 @@
       <c r="Y866" s="3"/>
       <c r="Z866" s="3"/>
     </row>
-    <row r="867" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -24756,7 +25672,7 @@
       <c r="Y867" s="3"/>
       <c r="Z867" s="3"/>
     </row>
-    <row r="868" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -24784,7 +25700,7 @@
       <c r="Y868" s="3"/>
       <c r="Z868" s="3"/>
     </row>
-    <row r="869" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -24812,7 +25728,7 @@
       <c r="Y869" s="3"/>
       <c r="Z869" s="3"/>
     </row>
-    <row r="870" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -24840,7 +25756,7 @@
       <c r="Y870" s="3"/>
       <c r="Z870" s="3"/>
     </row>
-    <row r="871" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -24868,7 +25784,7 @@
       <c r="Y871" s="3"/>
       <c r="Z871" s="3"/>
     </row>
-    <row r="872" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -24896,7 +25812,7 @@
       <c r="Y872" s="3"/>
       <c r="Z872" s="3"/>
     </row>
-    <row r="873" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -24924,7 +25840,7 @@
       <c r="Y873" s="3"/>
       <c r="Z873" s="3"/>
     </row>
-    <row r="874" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -24952,7 +25868,7 @@
       <c r="Y874" s="3"/>
       <c r="Z874" s="3"/>
     </row>
-    <row r="875" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -24980,7 +25896,7 @@
       <c r="Y875" s="3"/>
       <c r="Z875" s="3"/>
     </row>
-    <row r="876" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -25008,7 +25924,7 @@
       <c r="Y876" s="3"/>
       <c r="Z876" s="3"/>
     </row>
-    <row r="877" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -25036,7 +25952,7 @@
       <c r="Y877" s="3"/>
       <c r="Z877" s="3"/>
     </row>
-    <row r="878" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -25064,7 +25980,7 @@
       <c r="Y878" s="3"/>
       <c r="Z878" s="3"/>
     </row>
-    <row r="879" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -25092,7 +26008,7 @@
       <c r="Y879" s="3"/>
       <c r="Z879" s="3"/>
     </row>
-    <row r="880" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -25120,7 +26036,7 @@
       <c r="Y880" s="3"/>
       <c r="Z880" s="3"/>
     </row>
-    <row r="881" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -25148,7 +26064,7 @@
       <c r="Y881" s="3"/>
       <c r="Z881" s="3"/>
     </row>
-    <row r="882" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -25176,7 +26092,7 @@
       <c r="Y882" s="3"/>
       <c r="Z882" s="3"/>
     </row>
-    <row r="883" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -25204,7 +26120,7 @@
       <c r="Y883" s="3"/>
       <c r="Z883" s="3"/>
     </row>
-    <row r="884" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -25232,7 +26148,7 @@
       <c r="Y884" s="3"/>
       <c r="Z884" s="3"/>
     </row>
-    <row r="885" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -25260,7 +26176,7 @@
       <c r="Y885" s="3"/>
       <c r="Z885" s="3"/>
     </row>
-    <row r="886" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -25288,7 +26204,7 @@
       <c r="Y886" s="3"/>
       <c r="Z886" s="3"/>
     </row>
-    <row r="887" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -25316,7 +26232,7 @@
       <c r="Y887" s="3"/>
       <c r="Z887" s="3"/>
     </row>
-    <row r="888" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -25344,7 +26260,7 @@
       <c r="Y888" s="3"/>
       <c r="Z888" s="3"/>
     </row>
-    <row r="889" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -25372,7 +26288,7 @@
       <c r="Y889" s="3"/>
       <c r="Z889" s="3"/>
     </row>
-    <row r="890" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -25400,7 +26316,7 @@
       <c r="Y890" s="3"/>
       <c r="Z890" s="3"/>
     </row>
-    <row r="891" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -25428,7 +26344,7 @@
       <c r="Y891" s="3"/>
       <c r="Z891" s="3"/>
     </row>
-    <row r="892" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -25456,7 +26372,7 @@
       <c r="Y892" s="3"/>
       <c r="Z892" s="3"/>
     </row>
-    <row r="893" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -25484,7 +26400,7 @@
       <c r="Y893" s="3"/>
       <c r="Z893" s="3"/>
     </row>
-    <row r="894" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -25512,7 +26428,7 @@
       <c r="Y894" s="3"/>
       <c r="Z894" s="3"/>
     </row>
-    <row r="895" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -25540,7 +26456,7 @@
       <c r="Y895" s="3"/>
       <c r="Z895" s="3"/>
     </row>
-    <row r="896" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -25568,7 +26484,7 @@
       <c r="Y896" s="3"/>
       <c r="Z896" s="3"/>
     </row>
-    <row r="897" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -25596,7 +26512,7 @@
       <c r="Y897" s="3"/>
       <c r="Z897" s="3"/>
     </row>
-    <row r="898" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -25624,7 +26540,7 @@
       <c r="Y898" s="3"/>
       <c r="Z898" s="3"/>
     </row>
-    <row r="899" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -25652,7 +26568,7 @@
       <c r="Y899" s="3"/>
       <c r="Z899" s="3"/>
     </row>
-    <row r="900" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -25680,7 +26596,7 @@
       <c r="Y900" s="3"/>
       <c r="Z900" s="3"/>
     </row>
-    <row r="901" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -25708,7 +26624,7 @@
       <c r="Y901" s="3"/>
       <c r="Z901" s="3"/>
     </row>
-    <row r="902" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -25736,7 +26652,7 @@
       <c r="Y902" s="3"/>
       <c r="Z902" s="3"/>
     </row>
-    <row r="903" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -25764,7 +26680,7 @@
       <c r="Y903" s="3"/>
       <c r="Z903" s="3"/>
     </row>
-    <row r="904" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -25792,7 +26708,7 @@
       <c r="Y904" s="3"/>
       <c r="Z904" s="3"/>
     </row>
-    <row r="905" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -25820,7 +26736,7 @@
       <c r="Y905" s="3"/>
       <c r="Z905" s="3"/>
     </row>
-    <row r="906" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -25848,7 +26764,7 @@
       <c r="Y906" s="3"/>
       <c r="Z906" s="3"/>
     </row>
-    <row r="907" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -25876,7 +26792,7 @@
       <c r="Y907" s="3"/>
       <c r="Z907" s="3"/>
     </row>
-    <row r="908" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -25904,7 +26820,7 @@
       <c r="Y908" s="3"/>
       <c r="Z908" s="3"/>
     </row>
-    <row r="909" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -25932,7 +26848,7 @@
       <c r="Y909" s="3"/>
       <c r="Z909" s="3"/>
     </row>
-    <row r="910" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -25960,7 +26876,7 @@
       <c r="Y910" s="3"/>
       <c r="Z910" s="3"/>
     </row>
-    <row r="911" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -25988,7 +26904,7 @@
       <c r="Y911" s="3"/>
       <c r="Z911" s="3"/>
     </row>
-    <row r="912" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -26016,7 +26932,7 @@
       <c r="Y912" s="3"/>
       <c r="Z912" s="3"/>
     </row>
-    <row r="913" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -26044,7 +26960,7 @@
       <c r="Y913" s="3"/>
       <c r="Z913" s="3"/>
     </row>
-    <row r="914" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -26072,7 +26988,7 @@
       <c r="Y914" s="3"/>
       <c r="Z914" s="3"/>
     </row>
-    <row r="915" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -26100,7 +27016,7 @@
       <c r="Y915" s="3"/>
       <c r="Z915" s="3"/>
     </row>
-    <row r="916" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -26128,7 +27044,7 @@
       <c r="Y916" s="3"/>
       <c r="Z916" s="3"/>
     </row>
-    <row r="917" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -26156,7 +27072,7 @@
       <c r="Y917" s="3"/>
       <c r="Z917" s="3"/>
     </row>
-    <row r="918" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -26184,7 +27100,7 @@
       <c r="Y918" s="3"/>
       <c r="Z918" s="3"/>
     </row>
-    <row r="919" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -26212,7 +27128,7 @@
       <c r="Y919" s="3"/>
       <c r="Z919" s="3"/>
     </row>
-    <row r="920" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -26240,7 +27156,7 @@
       <c r="Y920" s="3"/>
       <c r="Z920" s="3"/>
     </row>
-    <row r="921" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -26268,7 +27184,7 @@
       <c r="Y921" s="3"/>
       <c r="Z921" s="3"/>
     </row>
-    <row r="922" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -26296,7 +27212,7 @@
       <c r="Y922" s="3"/>
       <c r="Z922" s="3"/>
     </row>
-    <row r="923" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -26324,7 +27240,7 @@
       <c r="Y923" s="3"/>
       <c r="Z923" s="3"/>
     </row>
-    <row r="924" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -26352,7 +27268,7 @@
       <c r="Y924" s="3"/>
       <c r="Z924" s="3"/>
     </row>
-    <row r="925" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -26380,7 +27296,7 @@
       <c r="Y925" s="3"/>
       <c r="Z925" s="3"/>
     </row>
-    <row r="926" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -26408,7 +27324,7 @@
       <c r="Y926" s="3"/>
       <c r="Z926" s="3"/>
     </row>
-    <row r="927" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -26436,7 +27352,7 @@
       <c r="Y927" s="3"/>
       <c r="Z927" s="3"/>
     </row>
-    <row r="928" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -26464,7 +27380,7 @@
       <c r="Y928" s="3"/>
       <c r="Z928" s="3"/>
     </row>
-    <row r="929" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -26492,7 +27408,7 @@
       <c r="Y929" s="3"/>
       <c r="Z929" s="3"/>
     </row>
-    <row r="930" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -26520,7 +27436,7 @@
       <c r="Y930" s="3"/>
       <c r="Z930" s="3"/>
     </row>
-    <row r="931" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -26548,7 +27464,7 @@
       <c r="Y931" s="3"/>
       <c r="Z931" s="3"/>
     </row>
-    <row r="932" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -26578,7 +27494,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" display="https://www.amazon.in/Samsung-Smartphone-Titanium-Storage-Included/dp/B0DSKMKJV5/ref=sr_1_3?crid=1LYSSGDKQ9KGQ&amp;dib=eyJ2IjoiMSJ9.6F9zxmqbhCO38LI-LW5u6uX5p_i9BhrpRmOubwMF6wjPDIO6VZkyfmdBNJz4oEp1n-wsQhHaCVuyrZXbVnKaX4XlxHTtW-aVZ9kFV_8e8489N8p048SHSJ19GWFAWIIldOyJ0kFxNaZeFqctwXdSfXP94sJV8txJrNV3EqzCtVZ5aIMSBoGMkkcCfY7qtQSOQxyVVP4Qw4B4jcwbD4mqfo9J4Aeck72a52mXj7sjzNk.v2XhDgp1crT3P9vuf34bKRiz-zb-AbcLZ7xiomulUBg&amp;dib_tag=se&amp;keywords=Samsung+Galaxy+S25+Ultra&amp;qid=1748551919&amp;sprefix=samsung+galaxy+s25+ultra,aps,513&amp;sr=8-3" xr:uid="{371BD03B-B8E1-984F-9492-24888A668D04}"/>
+    <hyperlink ref="B9" r:id="rId1" display="https://www.amazon.in/Samsung-Galaxy-Smartphone-Icyblue-Storage/dp/B0DSBVGKVF/ref=sr_1_3?crid=I1E29QDL1XES&amp;dib=eyJ2IjoiMSJ9.u3oNRuk1su5sLZB-iUGkvtUBUZz4Z2nGwya0IdTlHvyse9doMIDoqhH16srMYyvQMoMQKPtxbCsdMNQfEn43vkt7intmZPvFPayovsMNiPl8GIXxHEJQHRd4tTuFejYLY0JR13LHouBOB1SdqjbxRW98AnE92-fE5TPgxzLIjgkpD5P4sO0yfQpgPjFnBEYGejM3YKuHUm8vglPV_ga3cQedPGwKGdXOf6evXd2mJgQ.poUyX9VegdyHE_GTK8Fz4m8sCqXwVIbhOFTrDvvDRzU&amp;dib_tag=se&amp;keywords=samsung+s25&amp;qid=1748578880&amp;sprefix=samsung+s25+%2Caps%2C247&amp;sr=8-3" xr:uid="{A6B15814-3511-430F-8E35-A41D2D4D7FC6}"/>
+    <hyperlink ref="B10" r:id="rId2" display="https://www.amazon.in/iPhone-16-Pro-Max-256/dp/B0DGHYPFYB/ref=sr_1_1?crid=2BS4RVTR4LLWD&amp;dib=eyJ2IjoiMSJ9.Ka89qhdpabB3NoR8D6tI4VHFx66I8q7spoqlJKA0Kl7QZoiJeiYE6PyvLKYLAe93k4mJknAUIzStYdUebQTQd5GNvcyrAOzKHHeSuaUGh63Mny0U1TdoRAwWE1GsMtgxwGbYAyebYoYAUgBKgjhvIforHKBmw3FBxEGEK_DsiVk97fA0O2hYqcWmzDGVwLuBWthQHbdS-FHwssKHX6ga7NAHOK_MBOwGAH6mfx_Pn1U.AFUuo8c8s4O_sOOy1jYbLKUZaqsg0BNB5UulpUF4n6k&amp;dib_tag=se&amp;keywords=iphone%2B16%2Bpromax&amp;qid=1748578957&amp;sprefix=iphone%2B16%2Bpro%2Caps%2C247&amp;sr=8-1&amp;th=1" xr:uid="{9EB73D91-6A58-41A8-ADE5-042C86BF151F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
